--- a/mistral_translate_work/split_by_prompt/excel/skill_description/lang_multi_text/lang_multi_text__skill_description__part_0026.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/skill_description/lang_multi_text/lang_multi_text__skill_description__part_0026.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt; Khi khiên tạo bởi Phản Đòn Định Thời còn hiệu lực, sát thương Hỗn Loạn gây ra bởi Phản Đòn Định Thời sẽ tăng {0}.</t>
+          <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt; Khi khiên tạo bởi Phản Đòn Định Thời còn hiệu lực, DMG Hỗn Loạn gây ra bởi Phản Đòn Định Thời sẽ tăng {0}.</t>
         </is>
       </c>
     </row>
@@ -639,7 +639,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt; Khi khiên tạo bởi Resonance Circuit còn hiệu lực, sát thương Hỗn Loạn gây ra bởi Phản Đòn sẽ tăng đáng kể.</t>
+          <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt; Khi khiên tạo bởi Resonance Circuit còn hiệu lực, DMG Hỗn Loạn gây ra bởi Phản Đòn sẽ tăng đáng kể.</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Khi có lá chắn, tấn công mục tiêu sẽ kích hoạt "Effect Bùng Nổ Băng", gây 200% Glacio DMG. Hiệu ứng này chỉ kích hoạt một lần mỗi giây.</t>
+          <t>Khi có lá chắn, tấn công mục tiêu sẽ kích hoạt "Hiệu Ứng Bùng Nổ Băng", gây 200% Sát Thương Glacio. Hiệu ứng này chỉ kích hoạt một lần mỗi giây.</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Đòn tấn công sẽ kích hoạt "Effect Iceburst" khi có khiên bảo vệ.</t>
+          <t>Đòn tấn công sẽ kích hoạt "Hiệu Ứng Iceburst" khi có khiên bảo vệ.</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Hệ số Sát Thương của "Effect Bùng Nổ Băng" tăng thêm 100%. Khi mục tiêu bị áp dụng "Effect Bùng Nổ Băng" hai lần, chúng sẽ bị đóng băng trong 3 giây. Kẻ địch cấp Overlord và Calamity không thể bị đóng băng.</t>
+          <t>Hệ số Sát Thương của "Hiệu Ứng Bùng Nổ Băng" tăng thêm 100%. Khi mục tiêu bị áp dụng "Hiệu Ứng Bùng Nổ Băng" hai lần, chúng sẽ bị đóng băng trong 3 giây. Kẻ địch cấp Overlord và Calamity không thể bị đóng băng.</t>
         </is>
       </c>
     </row>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Hệ số sát thương Hiệu ứng Bùng Nổ Băng được tăng cường. Mục tiêu bị trúng Hiệu ứng Bùng Nổ Băng hai lần sẽ bị đóng băng trong 3 giây.</t>
+          <t>Hệ số DMG Hiệu ứng Bùng Nổ Băng được tăng cường. Mục tiêu bị trúng Hiệu ứng Bùng Nổ Băng hai lần sẽ bị đóng băng trong 3 giây.</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Inferno Rider tăng 50% sát thương kỹ năng Echo toàn bộ của Inferno Rider</t>
+          <t>Kỵ Sĩ Hỏa Ngục tăng 50% sát thương kỹ năng Echo toàn bộ của Kỵ Sĩ Hỏa Ngục</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Trigger "Hồi Chuông Vang Dội" khi nhận được khiên. Hồi Chuông Vang Dội tạo ra "Effect Bùng Nổ Băng" trong phạm vi lớn hơn, gây 1500% Glacio DMG lên kẻ địch xung quanh và đóng băng chúng ngay lập tức trong 5 giây. Kẻ địch cấp Overlord và Calamity không bị đóng băng. Có thể kích hoạt mỗi 3 giây một lần.</t>
+          <t>Kích hoạt "Hồi Chuông Vang Dội" khi nhận được khiên. Hồi Chuông Vang Dội tạo ra "Hiệu Ứng Bùng Nổ Băng" trong phạm vi lớn hơn, gây 1500% Sát Thương Glacio lên kẻ địch xung quanh và đóng băng chúng ngay lập tức trong 5 giây. Kẻ địch cấp Overlord và Calamity không bị đóng băng. Có thể kích hoạt mỗi 3 giây một lần.</t>
         </is>
       </c>
     </row>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Trigger "Hồi Chuông Vang Dội" khi nhận được khiên.</t>
+          <t>Kích hoạt "Hồi Chuông Vang Dội" khi nhận được khiên.</t>
         </is>
       </c>
     </row>
@@ -1355,7 +1355,7 @@
       <c r="M14" t="inlineStr">
         <is>
           <t>[
-Rùa Địa Chất Mang Chuông] [Đòn Hợp Tác] Rùa Địa Chất Mang Chuông sẽ gây sát thương một lần khi Resonance Skill kết thúc.</t>
+Rùa Địa Chất Mang Chuông] [Đòn Hợp Tác] Rùa Địa Chất Mang Chuông sẽ gây DMG một lần khi Resonance Skill kết thúc.</t>
         </is>
       </c>
     </row>
@@ -1487,7 +1487,7 @@
       <c r="M16" t="inlineStr">
         <is>
           <t>[
-Rùa Địa Chất Mang Chuông] [Sát Thương Đóng Băng] Khi sử dụng Kỹ Năng Vọng Âm, gây thêm sát thương lên kẻ địch bị đóng băng.</t>
+Rùa Địa Chất Mang Chuông] [Sát Thương Đóng Băng] Khi sử dụng Kỹ Năng Vọng Âm, gây thêm DMG lên kẻ địch bị đóng băng.</t>
         </is>
       </c>
     </row>
@@ -1554,9 +1554,9 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Sau khi dùng Basic Attack, Heavy Attack, Dodge Counter, Resonance Skill, Resonance Liberation, Intro Skill hoặc Kỹ Năng Echo, sẽ nhận được một dấu hiệu đặc biệt kéo dài 4 giây. Dấu hiệu này có thể cộng dồn tối đa 10 lần và sẽ ngừng cộng dồn trong 4 giây khi đạt tối đa. Khi đạt tối đa, triệu hồi Inferno Rider thực hiện 3 Đòn Phối Hợp, gây Fusion DMG bằng 807.6% Attack và gây 1 tầng Bỏng lên mục tiêu với mỗi đòn.
+          <t>Sau khi dùng Đòn Cơ Bản, Đòn Nặng, Dodge Counter Tránh, Resonance Skill, Resonance Liberation, Kỹ Năng Khởi Động hoặc Kỹ Năng Echo, sẽ nhận được một dấu hiệu đặc biệt kéo dài 4 giây. Dấu hiệu này có thể cộng dồn tối đa 10 lần và sẽ ngừng cộng dồn trong 4 giây khi đạt tối đa. Khi đạt tối đa, triệu hồi Kỵ Sĩ Hỏa Ngục thực hiện 3 Đòn Phối Hợp, gây Sát Thương Fusion bằng 807.6% ATK và gây 1 tầng Bỏng lên mục tiêu với mỗi đòn.
 - Bỏng:
-Kéo dài 8 giây, tối đa 5 tầng. Ở tầng 1/2/3/4/5, gây Fusion DMG mỗi giây bằng 10%/20%/30%/40%/50% Attack.</t>
+Kéo dài 8 giây, tối đa 5 tầng. Ở tầng 1/2/3/4/5, gây Sát Thương Fusion mỗi giây bằng 10%/20%/30%/40%/50% ATK.</t>
         </is>
       </c>
     </row>
@@ -1755,7 +1755,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Sát thương của Inferno Rider tăng thêm 50%. Khi tấn công mục tiêu bị Đốt Cháy, Cooldown chiêu của Kỹ Năng Echo giảm 1 giây. Hiệu ứng này chỉ kích hoạt tối đa 1 lần mỗi giây.</t>
+          <t>DMG của Inferno Rider tăng thêm 50%. Khi tấn công mục tiêu bị Đốt Cháy, thời gian hồi chiêu của Kỹ Năng Echo giảm 1 giây. Hiệu ứng này chỉ kích hoạt tối đa 1 lần mỗi giây.</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Cooldown chiêu Skill Cộng hưởng giảm khi tấn công mục tiêu bị "Bỏng".</t>
+          <t>Thời gian hồi chiêu Kỹ năng Cộng hưởng giảm khi tấn công mục tiêu bị "Bỏng".</t>
         </is>
       </c>
     </row>
@@ -1886,7 +1886,7 @@
       <c r="M22" t="inlineStr">
         <is>
           <t>[
-Rùa Địa Chất Mang Chuông] Khi có Shield, Resonance Skill sẽ giảm Cooldown chiêu của Kỹ Năng Vọng Âm.</t>
+Rùa Địa Chất Mang Chuông] Khi có Khiên, Resonance Skill sẽ giảm thời gian hồi chiêu của Kỹ Năng Vọng Âm.</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Các đòn tấn công liên tiếp kích hoạt "Đòn Phối Hợp" của "Inferno Rider".</t>
+          <t>Các đòn tấn công liên tiếp kích hoạt "Đòn Phối Hợp" của "Kỵ Sĩ Hỏa Ngục".</t>
         </is>
       </c>
     </row>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Summon đòn tấn công phối hợp cùng Crownless khi bạn thực hiện Heavy Attack.</t>
+          <t>Triệu hồi đòn tấn công phối hợp cùng Crownless khi bạn thực hiện Đòn Tấn Công Mạnh.</t>
         </is>
       </c>
     </row>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Summon đòn tấn công phối hợp cùng Crownless khi bạn gây sát thương.</t>
+          <t>Triệu hồi đòn tấn công phối hợp cùng Crownless khi bạn gây DMG.</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Nhận thêm 8% "Năng Lượng Vương Miện" khi đánh bại kẻ địch ở trạng thái bình thường. Gây thêm 100% sát thương khi ở trạng thái "Biến Hình".</t>
+          <t>Nhận thêm 8% "Năng Lượng Vương Miện" khi đánh bại kẻ địch ở trạng thái bình thường. Gây thêm 100% DMG khi ở trạng thái "Biến Hình".</t>
         </is>
       </c>
     </row>
@@ -2276,7 +2276,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Mở khóa Resonance Skill của Crownless. Tăng cường trạng thái biến hình.</t>
+          <t>Mở khóa Resonance Skill của Vô Vương. Tăng cường trạng thái biến hình.</t>
         </is>
       </c>
     </row>
@@ -2406,7 +2406,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Mở khóa Resonance Liberation của Crownless. Tăng cường trạng thái "Shapeshift".</t>
+          <t>Mở khóa Resonance Liberation của Vô Vương. Tăng cường trạng thái "Biến Hình".</t>
         </is>
       </c>
     </row>
@@ -2602,7 +2602,7 @@
       <c r="M33" t="inlineStr">
         <is>
           <t>[
-Rùa Địa Chất Mang Chuông] [Cooldown] Tấn công kẻ địch bị đóng băng sẽ giảm 50% Cooldown chiêu của Kỹ Năng Vọng Âm (hiệu ứng này có Cooldown 15 giây).</t>
+Rùa Địa Chất Mang Chuông] [Hồi Chiêu] Tấn công kẻ địch bị đóng băng sẽ giảm 50% Thời gian hồi chiêu của Kỹ Năng Vọng Âm (hiệu ứng này có Thời gian hồi 15 giây).</t>
         </is>
       </c>
     </row>
@@ -2667,7 +2667,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Mở khóa một Resonance Skill đặc biệt dưới dạng Crownless. Biến hình thành Crownless sẽ phục hồi {0} HP tối đa. Gây thêm {1} DMG dưới dạng Crownless.</t>
+          <t>Mở khóa một Resonance Skill đặc biệt dưới dạng Vô Vương. Biến hình thành Vô Vương sẽ phục hồi {0} HP tối đa. Gây thêm {1} DMG khi ở dạng Vô Vương.</t>
         </is>
       </c>
     </row>
@@ -2732,7 +2732,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Mở khóa một Resonance Liberation đặc biệt dưới dạng Crownless. Resonance Liberation này là đòn kết thúc của Crownless. Bạn sẽ luôn ở dạng Crownless khi sử dụng Resonance Liberation này, nhưng sẽ thoát khỏi dạng Crownless ngay sau khi hoàn thành. Gây thêm {0} DMG dưới dạng Crownless.</t>
+          <t>Mở khóa một Kỹ Năng Resonance Liberation đặc biệt dưới dạng Vô Vương. Kỹ Năng Resonance Liberation này là đòn kết thúc của Vô Vương. Khi sử dụng, ngươi sẽ luôn ở dạng Vô Vương, nhưng sẽ thoát khỏi dạng này ngay sau khi kỹ năng kết thúc. Gây thêm {0} DMG khi ở dạng Vô Vương.</t>
         </is>
       </c>
     </row>
@@ -2863,7 +2863,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt; Đòn tấn công giữa không khí gây thêm Electro Damage lên kẻ địch mang "Dấu Trừng Phạt". Lượng Sát Thương này tương đương với Resonance Liberation. Hiệu ứng này có Cooldown chiêu {0} giây. Cooldown chiêu sẽ được đặt lại khi thi triển Chameleon Cipher.</t>
+          <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt; Đòn tấn công giữa không khí gây thêm Sát Thương Electro lên kẻ địch mang "Dấu Trừng Phạt". Lượng Sát Thương này tương đương với Resonance Liberation. Hiệu ứng này có thời gian hồi chiêu {0} giây. Thời gian hồi chiêu sẽ được đặt lại khi thi triển Chameleon Cipher.</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt; Đòn tấn công giữa không khí gây thêm lượng lớn Sát Thương lên kẻ địch mang Dấu Trừng Phạt, và Cooldown chiêu của lượng Sát Thương thêm này sẽ được đặt lại khi thi triển Heavy Attack được tăng cường.</t>
+          <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt; Đòn tấn công giữa không khí gây thêm lượng lớn Sát Thương lên kẻ địch mang Dấu Trừng Phạt, và Thời gian hồi chiêu của lượng Sát Thương thêm này sẽ được đặt lại khi thi triển Đòn Heavy Attack được tăng cường.</t>
         </is>
       </c>
     </row>
@@ -2993,7 +2993,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Trigger Đồng Điệu Bùng Nổ của 2 Liên Kết khác nhau</t>
+          <t>Kích hoạt Đồng Điệu Bùng Nổ của 2 Liên Kết khác nhau</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Trigger Đồng Điệu Bùng Nổ của 4 Liên Kết khác nhau</t>
+          <t>Kích hoạt Đồng Điệu Bùng Nổ của 4 Liên Kết khác nhau</t>
         </is>
       </c>
     </row>
@@ -3123,7 +3123,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Trigger Đồng Điệu Bùng Nổ của 8 Liên Kết khác nhau</t>
+          <t>Kích hoạt Đồng Điệu Bùng Nổ của 8 Liên Kết khác nhau</t>
         </is>
       </c>
     </row>
@@ -3188,7 +3188,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Tiêu tốn tổng cộng 200 Cuộn Film.</t>
+          <t>Tiêu tốn tổng cộng 200 Cuộn Phim.</t>
         </is>
       </c>
     </row>
@@ -3253,7 +3253,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Tiêu tốn tổng cộng 400 Cuộn Film.</t>
+          <t>Tiêu tốn tổng cộng 400 Cuộn Phim.</t>
         </is>
       </c>
     </row>
@@ -3578,7 +3578,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Cooldown kỹ năng Cộng hưởng giảm 30%.</t>
+          <t>Thời gian hồi kỹ năng Cộng hưởng giảm 30%.</t>
         </is>
       </c>
     </row>
@@ -3643,7 +3643,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Restore 7% HP tối đa khi bước vào Vùng Ký Ức</t>
+          <t>Hồi phục 7% HP tối đa khi bước vào Vùng Ký Ức</t>
         </is>
       </c>
     </row>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Sát thương gây ra tăng thêm 15% trong Depths of Illusive Realm.</t>
+          <t>DMG gây ra tăng thêm 15% trong Depths of Illusive Realm.</t>
         </is>
       </c>
     </row>
@@ -4163,7 +4163,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Dodge thành công sẽ hồi phục 5% HP tối đa. Có thể kích hoạt 1 lần mỗi 3 giây.</t>
+          <t>Né thành công sẽ hồi phục 5% HP tối đa. Có thể kích hoạt 1 lần mỗi 3 giây.</t>
         </is>
       </c>
     </row>
@@ -4228,7 +4228,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Mỗi giây ở hạng A trở lên, tăng 10% sát thương gây ra trong 2 giây, tối đa 10 tầng.</t>
+          <t>Mỗi giây ở hạng A trở lên, tăng 10% DMG gây ra trong 2 giây, tối đa 10 tầng.</t>
         </is>
       </c>
     </row>
@@ -4358,7 +4358,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Cooldown kỹ năng Cộng hưởng giảm 30%.</t>
+          <t>Thời gian hồi kỹ năng Cộng hưởng giảm 30%.</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Increase HP thêm 35% trong Depths of Illusive Realm.</t>
+          <t>Tăng HP thêm 35% trong Depths of Illusive Realm.</t>
         </is>
       </c>
     </row>
@@ -4488,7 +4488,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Giảm 20% sát thương nhận vào tại Vực Ảo Ảnh.</t>
+          <t>Giảm 20% DMG nhận vào tại Vực Ảo Ảnh.</t>
         </is>
       </c>
     </row>
@@ -4553,7 +4553,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Dodge thành công sẽ hồi phục 5% HP tối đa. Có thể kích hoạt 1 lần mỗi 3 giây.</t>
+          <t>Né thành công sẽ hồi phục 5% HP tối đa. Có thể kích hoạt 1 lần mỗi 3 giây.</t>
         </is>
       </c>
     </row>
@@ -4618,7 +4618,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Increase HP thêm 25% trong Depths of Illusive Realm.</t>
+          <t>Tăng HP thêm 25% trong Depths of Illusive Realm.</t>
         </is>
       </c>
     </row>
@@ -4683,7 +4683,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Increase Phòng Ngự thêm 40% trong Depths of Illusive Realm.</t>
+          <t>Tăng Phòng Ngự thêm 40% trong Depths of Illusive Realm.</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Giảm 20% sát thương nhận vào tại Vực Ảo Ảnh.</t>
+          <t>Giảm 20% DMG nhận vào tại Vực Ảo Ảnh.</t>
         </is>
       </c>
     </row>
@@ -4813,7 +4813,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Dodge thành công sẽ tạo ra lá chắn tương đương 50% HP tối đa trong 3 giây. Có thể kích hoạt mỗi 6 giây một lần.</t>
+          <t>Né thành công sẽ tạo ra lá chắn tương đương 50% HP tối đa trong 3 giây. Có thể kích hoạt mỗi 6 giây một lần.</t>
         </is>
       </c>
     </row>
@@ -4878,7 +4878,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Dodge thành công sẽ giảm 2 giây Cooldown chiêu của Resonance Skill và Resonance Liberation.</t>
+          <t>Né thành công sẽ giảm 2 giây Thời gian hồi chiêu của Resonance Skill và Resonance Liberation.</t>
         </is>
       </c>
     </row>
@@ -4943,7 +4943,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Increase Crit. DMG thêm 10% trong Độ Sâu Ảo Tưởng.</t>
+          <t>Tăng Crit. DMG thêm 10% trong Độ Sâu Ảo Tưởng.</t>
         </is>
       </c>
     </row>
@@ -5073,7 +5073,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Increase Crit. DMG thêm 15% trong Độ Sâu Ảo Tưởng.</t>
+          <t>Tăng Crit. DMG thêm 15% trong Độ Sâu Ảo Tưởng.</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Giảm 30% Cooldown chiêu Resonance Skill.</t>
+          <t>Giảm 30% Thời gian hồi chiêu Resonance Skill.</t>
         </is>
       </c>
     </row>
@@ -5268,7 +5268,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Increase Crit. Rate thêm 20% trong Độ Sâu Ảo Tưởng. Phần Crit. Rate vượt mức sẽ chuyển thành Crit. DMG theo tỷ lệ 1:1.</t>
+          <t>Tăng Crit. Rate thêm 20% trong Độ Sâu Ảo Tưởng. Phần Crit. Rate vượt mức sẽ chuyển thành Crit. DMG theo tỷ lệ 1:1.</t>
         </is>
       </c>
     </row>
@@ -5333,7 +5333,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Increase HP thêm 50% trong Depths of Illusive Realm.</t>
+          <t>Tăng HP thêm 50% trong Depths of Illusive Realm.</t>
         </is>
       </c>
     </row>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Increase 10% Tấn Công trong Depths of Illusive Realm.</t>
+          <t>Tăng 10% ATK trong Depths of Illusive Realm.</t>
         </is>
       </c>
     </row>
@@ -5463,7 +5463,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Increase 10% Tấn Công trong Depths of Illusive Realm.</t>
+          <t>Tăng 10% ATK trong Depths of Illusive Realm.</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Increase 15% Tấn Công trong Depths of Illusive Realm.</t>
+          <t>Tăng 15% ATK trong Depths of Illusive Realm.</t>
         </is>
       </c>
     </row>
@@ -5593,7 +5593,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Increase Tấn Công thêm 25% trong Vực Ảo Ảnh.</t>
+          <t>Tăng ATK thêm 25% trong Vực Ảo Ảnh.</t>
         </is>
       </c>
     </row>
@@ -5723,7 +5723,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Increase Crit. Rate thêm 16% trong Độ Sâu Ảo Tưởng.</t>
+          <t>Tăng Crit. Rate thêm 16% trong Độ Sâu Ảo Tưởng.</t>
         </is>
       </c>
     </row>
@@ -5983,7 +5983,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Increase Crit. DMG thêm 25% trong Độ Sâu Ảo Tưởng.</t>
+          <t>Tăng Crit. DMG thêm 25% trong Độ Sâu Ảo Tưởng.</t>
         </is>
       </c>
     </row>
@@ -6048,7 +6048,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Heavy Attack]&lt;/color&gt; Heavy Attack: Stormy Strike tạo ra Tổ Gió.</t>
+          <t>&lt;color=#c49e55&gt;[Đòn Heavy Attack]&lt;/color&gt; Đòn Heavy Attack: Stormy Strike tạo ra Tổ Gió.</t>
         </is>
       </c>
     </row>
@@ -6113,7 +6113,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Special Enhancement]&lt;/color&gt; Tất cả Tổ Gió tăng sát thương và hiệu ứng kéo.</t>
+          <t>&lt;color=#c49e55&gt;[Tăng Cường Đặc Biệt]&lt;/color&gt; Tất cả Tổ Gió tăng sát thương và hiệu ứng kéo.</t>
         </is>
       </c>
     </row>
@@ -6243,7 +6243,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Heavy Attack]&lt;/color&gt; Heavy Attack: Zephyr Song tạo ra Tổ Gió.</t>
+          <t>&lt;color=#c49e55&gt;[Đòn Heavy Attack]&lt;/color&gt; Đòn Heavy Attack: Zephyr Song tạo ra Tổ Gió.</t>
         </is>
       </c>
     </row>
@@ -6308,7 +6308,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt;&lt;color=#c49e55&gt;[Effect Enhancement]&lt;/color&gt; Tạo ra "Trường Gió" sẽ nhận được "Sức Mạnh Gió", và khi sử dụng "Giải Phóng Feather", phạm vi và sát thương của đòn tấn công sẽ tăng theo lượng "Sức Mạnh Gió" đã tiêu thụ.</t>
+          <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt;&lt;color=#c49e55&gt;[Tăng Cường Hiệu Ứng]&lt;/color&gt; Tạo ra "Trường Gió" sẽ nhận được "Sức Mạnh Gió", và khi sử dụng "Giải Phóng Lông Vũ", phạm vi và sát thương của đòn tấn công sẽ tăng theo lượng "Sức Mạnh Gió" đã tiêu thụ.</t>
         </is>
       </c>
     </row>
@@ -6373,7 +6373,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Forte Circuit]&lt;/color&gt; Đặt lại Cooldown chiêu của Skill Cộng hưởng sau khi sử dụng "Rơi lông vũ".</t>
+          <t>&lt;color=#ffd12f&gt;[Forte Circuit]&lt;/color&gt; Reset thời gian hồi chiêu của Kỹ năng Cộng hưởng sau khi sử dụng "Rơi lông vũ".</t>
         </is>
       </c>
     </row>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Resonance Liberation]&lt;/color&gt; Sau khi kích hoạt Resonance Liberation, bước vào trạng thái "Unlimited Firepower".</t>
+          <t>&lt;color=#c49e55&gt;[Resonance Liberation]&lt;/color&gt; Sau khi kích hoạt Resonance Liberation, bước vào trạng thái "Hỏa Lực Vô Hạn".</t>
         </is>
       </c>
     </row>
@@ -6958,7 +6958,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt; Dấu Trừng Phạt giảm {0} giây thời gian tồn tại. Sát Thương gây ra bởi "Đòn Phán Xét" nhận thêm {1} Electro DMG Bonus.</t>
+          <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt; Dấu Trừng Phạt giảm {0} giây thời gian tồn tại. Sát Thương gây ra bởi "Đòn Phán Xét" nhận thêm {1} Tăng Sát Thương Electro.</t>
         </is>
       </c>
     </row>
@@ -7023,7 +7023,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Basic Attack]&lt;/color&gt; Khi đánh dấu kẻ địch bằng Sinner's Mark, Basic Attack sẽ kích hoạt thêm Vụ Nổ Điện Từ.</t>
+          <t>&lt;color=#c49e55&gt;[Basic Attack]&lt;/color&gt; Khi đánh dấu kẻ địch bằng Dấu Ấn Tội Nhân, Basic Attack sẽ kích hoạt thêm Vụ Nổ Điện Từ.</t>
         </is>
       </c>
     </row>
@@ -7218,7 +7218,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt; Dấu Trừng Phạt tồn tại ngắn hơn, và Resonance Liberation gây Electro DMG tăng mạnh.</t>
+          <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt; Dấu Trừng Phạt tồn tại ngắn hơn, và Resonance Liberation gây Sát Thương Electro tăng mạnh.</t>
         </is>
       </c>
     </row>
@@ -7868,7 +7868,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>Tăng cường Resonance</t>
+          <t>Tăng Cường Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -7933,7 +7933,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Resonance Oversounding</t>
+          <t>Cộng Hưởng Vượt Ngưỡng</t>
         </is>
       </c>
     </row>
@@ -7998,7 +7998,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>Huanglong - Chương I: Resonance Đầu Tiên</t>
+          <t>Huanglong - Chương I: Cộng Hưởng Đầu Tiên</t>
         </is>
       </c>
     </row>
@@ -8063,7 +8063,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Damage Increase]&lt;/color&gt; Tấn Công tăng 50% sau khi sử dụng Grapple. Cooldown chiêu của Grapple giảm 5 giây.</t>
+          <t>&lt;color=#ffd12f&gt;[Tăng Sát Thương]&lt;/color&gt; ATK tăng 50% sau khi sử dụng Grapple. Thời gian hồi chiêu của Grapple giảm 5 giây.</t>
         </is>
       </c>
     </row>
@@ -8128,7 +8128,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Damage Increase]&lt;/color&gt; Tấn Công tăng vừa phải sau khi sử dụng Grapple. Cooldown chiêu Grapple giảm.</t>
+          <t>&lt;color=#ffd12f&gt;[Tăng Sát Thương]&lt;/color&gt; ATK tăng vừa phải sau khi sử dụng Móc Câu. Thời gian hồi chiêu Móc Câu giảm.</t>
         </is>
       </c>
     </row>
@@ -8193,7 +8193,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Shield]&lt;/color&gt; Nhận khiên sau khi sử dụng Grapple. Cooldown chiêu của Grapple giảm đi.</t>
+          <t>&lt;color=#ffd12f&gt;[Khiên]&lt;/color&gt; Nhận khiên sau khi sử dụng Móc Câu. Thời gian hồi chiêu của Móc Câu giảm đi.</t>
         </is>
       </c>
     </row>
@@ -8258,7 +8258,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Shield]&lt;/color&gt; Nhận khiên tương đương 5% HP tối đa sau khi sử dụng Grapple. Cooldown chiêu của Grapple giảm 5 giây.</t>
+          <t>&lt;color=#ffd12f&gt;[Khiên]&lt;/color&gt; Nhận khiên tương đương 5% HP tối đa sau khi sử dụng Móc Câu. Thời gian hồi chiêu của Móc Câu giảm 5 giây.</t>
         </is>
       </c>
     </row>
@@ -8583,7 +8583,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>Chọn Buff</t>
+          <t>Chọn Hiệu Ứng Tăng Cường</t>
         </is>
       </c>
     </row>
@@ -8648,7 +8648,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>Chủ lực gây DMG</t>
+          <t>Vai trò Sát Thương Chính</t>
         </is>
       </c>
     </row>
@@ -8713,7 +8713,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Efficiency Giao Hưởng</t>
+          <t>Hiệu Suất Giao Hưởng</t>
         </is>
       </c>
     </row>
@@ -8778,7 +8778,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>Sát thương Basic Attack</t>
+          <t>DMG Basic Attack</t>
         </is>
       </c>
     </row>
@@ -8843,7 +8843,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>Sát Thương Heavy Attack</t>
+          <t>Sát Thương Đòn Heavy Attack</t>
         </is>
       </c>
     </row>
@@ -9103,7 +9103,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>Khuếch đại DMG</t>
+          <t>Khuếch Đại Sát Thương</t>
         </is>
       </c>
     </row>
@@ -9168,7 +9168,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Khuếch đại Havoc DMG</t>
+          <t>Khuếch Đại Sát Thương Havoc</t>
         </is>
       </c>
     </row>
@@ -9233,7 +9233,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>Khuếch đại Aero DMG</t>
+          <t>Khuếch Đại Sát Thương Aero</t>
         </is>
       </c>
     </row>
@@ -9298,7 +9298,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>Khuếch đại Electro DMG</t>
+          <t>Khuếch Đại Sát Thương Electro</t>
         </is>
       </c>
     </row>
@@ -9363,7 +9363,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>Khuếch đại Fusion DMG</t>
+          <t>Khuếch Đại Sát Thương Hợp Thể</t>
         </is>
       </c>
     </row>
@@ -9428,7 +9428,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>Khuếch đại Glacio DMG</t>
+          <t>Khuếch Đại Sát Thương Băng giá</t>
         </is>
       </c>
     </row>
@@ -9493,7 +9493,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Khuếch đại Spectro DMG</t>
+          <t>Khuếch Đại Sát Thương Spectro</t>
         </is>
       </c>
     </row>
@@ -9558,7 +9558,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>Khuếch đại Sát thương Basic Attack</t>
+          <t>Khuếch đại DMG Basic Attack</t>
         </is>
       </c>
     </row>
@@ -9623,7 +9623,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>DMG Amplification Heavy Attack</t>
+          <t>Khuếch Đại Sát Thương Đòn Heavy Attack</t>
         </is>
       </c>
     </row>
@@ -9688,7 +9688,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>DMG Amplification Resonance Skill</t>
+          <t>Khuếch Đại Sát Thương Resonance Skill</t>
         </is>
       </c>
     </row>
@@ -9753,7 +9753,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>DMG Amplification Resonance Liberation</t>
+          <t>Khuếch Đại Sát Thương Resonance Liberation</t>
         </is>
       </c>
     </row>
@@ -9818,7 +9818,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>Erosion Aero</t>
+          <t>Aero Erosion</t>
         </is>
       </c>
     </row>
@@ -9948,7 +9948,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>Bùng Nổ Fusion</t>
+          <t>Fusion Burst</t>
         </is>
       </c>
     </row>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>Vui lòng trang bị tất cả chỉ số buff.</t>
+          <t>Vui lòng trang bị tất cả chỉ số tăng cường.</t>
         </is>
       </c>
     </row>
@@ -10208,7 +10208,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>Tăng tỷ lệ kích hoạt Eureka</t>
+          <t>Tỷ Lệ Kích Hoạt Eureka Tăng</t>
         </is>
       </c>
     </row>
@@ -10273,7 +10273,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>Sao ngạc nhiên thế? Đây là kỹ năng cơ bản của mọi đặc vụ ngầm. Shh... bí mật là trên hết.</t>
+          <t>Sao ngạc nhiên thế? Đây là kỹ năng cơ bản của mọi đặc vụ ngầm. Suỵt... bí mật là trên hết.</t>
         </is>
       </c>
     </row>
@@ -10338,7 +10338,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>Increase Điểm Đánh Giá Nguyện Ước</t>
+          <t>Tăng Điểm Đánh Giá Nguyện Ước</t>
         </is>
       </c>
     </row>
@@ -10406,8 +10406,8 @@
       <c r="M153" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Basic Attack]&lt;/color&gt; Crit. Rate tăng {0} và Crit. DMG tăng {1}. Basic Attack nhận các tăng cường sau:
-- Sau Stage 3 của Basic Attack, nếu dùng Basic Attack hoặc Dodge Phản Đòn đúng lúc sẽ kích hoạt Phản Đòn Chí.
-- Mỗi lần Basic Attack trúng mục tiêu, Cooldown chiêu của Resonance Skill giảm {2} giây.</t>
+- Sau Giai Đoạn 3 của Basic Attack, nếu dùng Basic Attack hoặc Né Tránh Phản Đòn đúng lúc sẽ kích hoạt Phản Đòn Chí.
+- Mỗi lần Basic Attack trúng mục tiêu, Thời gian hồi chiêu của Resonance Skill giảm {2} giây.</t>
         </is>
       </c>
     </row>
@@ -10476,9 +10476,9 @@
       <c r="M154" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt; "Gió Lặng" nhận được các tăng cường sau:
-- Tăng sát thương Resonance Skill thêm {0}.
+- DMG Bonus Resonance Skill thêm {0}.
 - Nếu kích hoạt thành công Phản Đòn Chí, nhận thêm {1} Chí.
-- Nếu sử dụng "Gió Lặng" ngay trước khi đòn tấn công trúng, coi như Phản Đòn Hoàn Hảo, nhận thêm {2} Chí và tạo ra Trường Lực Purification. Hiệu ứng này chỉ có thể kích hoạt mỗi {3} giây một lần.</t>
+- Nếu sử dụng "Gió Lặng" ngay trước khi đòn tấn công trúng, coi như Phản Đòn Hoàn Hảo, nhận thêm {2} Chí và tạo ra Trường Lực Thanh Tẩy. Hiệu ứng này chỉ có thể kích hoạt mỗi {3} giây một lần.</t>
         </is>
       </c>
     </row>
@@ -10549,7 +10549,7 @@
           <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt; Luân Xoay Chí Nguyên nhận các tăng cường sau:
 - Luân Xoay Chí Nguyên gây thêm {0} Sát Thương.
 - Khi kỹ năng đang hoạt động, mục tiêu trong phạm vi sẽ liên tục bị kéo về.
-- Sự tập trung Chí được đẩy nhanh để đạt tới Đại Chu Thiên: Ngoại Bộ, tung ra một cú Punch Đẩy Tăng Cường tấn công mục tiêu.</t>
+- Sự tập trung Chí được đẩy nhanh để đạt tới Đại Chu Thiên: Ngoại Bộ, tung ra một cú Đấm Đẩy Tăng Cường tấn công mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -10617,8 +10617,8 @@
       <c r="M156" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Liberation]&lt;/color&gt; Kích hoạt Resonance Liberation ban cho Nguyên Khí kéo dài {0} giây:
-- Khi gây sát thương, Aero RES DMG của mục tiêu bị bỏ qua {1}.
-- Cooldown chiêu của Resonance Skill giảm {2}. Kích hoạt Resonance Skill được coi là kích hoạt Phản Đòn Hoàn Hảo.</t>
+- Khi gây DMG, Kháng Sát Thương Aero của mục tiêu bị bỏ qua {1}.
+- Thời gian hồi chiêu của Resonance Skill giảm {2}. Kích hoạt Resonance Skill được coi là kích hoạt Phản Đòn Hoàn Hảo.</t>
         </is>
       </c>
     </row>
@@ -10943,7 +10943,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Resonance Liberation]&lt;/color&gt; Kích hoạt Trường Lực Purification sẽ nhận hiệu ứng tăng cường liên tục.</t>
+          <t>&lt;color=#c49e55&gt;[Resonance Liberation]&lt;/color&gt; Kích hoạt Trường Lực Thanh Tẩy sẽ nhận hiệu ứng tăng cường liên tục.</t>
         </is>
       </c>
     </row>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt; Sau khi sử dụng Resonance Skill, đòn Basic Attack tiếp theo trong {0} giây sẽ được thay thế bằng Kỹ Năng Nhanh: Heavy Attack - Kích Nổ, tăng khả năng kháng gián đoạn. Sát thương Bùng Nổ Băng tăng {1}.</t>
+          <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt; Sau khi sử dụng Resonance Skill, đòn Basic Attack tiếp theo trong {0} giây sẽ được thay thế bằng Kỹ Năng Nhanh: Heavy Attack - Kích Nổ, tăng khả năng kháng gián đoạn. DMG Bùng Nổ Băng tăng {1}.</t>
         </is>
       </c>
     </row>
@@ -11073,7 +11073,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Basic Attack]&lt;/color&gt; Basic Attack 5 tạo thêm một Ice Thorn. Sát thương Vụ Nổ Băng tăng thêm {0}.</t>
+          <t>&lt;color=#c49e55&gt;[Basic Attack]&lt;/color&gt; Basic Attack 5 tạo thêm một Gai Băng. DMG Vụ Nổ Băng tăng thêm {0}.</t>
         </is>
       </c>
     </row>
@@ -11138,7 +11138,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Heavy Attack]&lt;/color&gt; Sau khi Heavy Attack: Bùng Nổ trúng mục tiêu, Basic Attack tiếp theo trong {0} giây sẽ được thay thế bằng Heavy Attack Nhanh: Bùng Nổ, tăng khả năng chống gián đoạn và tạo thêm một Prism Băng Giá. Sát Thương Vụ Nổ Băng tăng {1}.</t>
+          <t>&lt;color=#c49e55&gt;[Heavy Attack]&lt;/color&gt; Sau khi Heavy Attack: Bùng Nổ trúng mục tiêu, Đòn Basic Attack tiếp theo trong {0} giây sẽ được thay thế bằng Heavy Attack Nhanh: Bùng Nổ, tăng khả năng chống gián đoạn và tạo thêm một Lăng Kính Băng Giá. Sát Thương Vụ Nổ Băng tăng {1}.</t>
         </is>
       </c>
     </row>
@@ -11203,7 +11203,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt; Có thể tự động nhận được Sự Thanh Khiết theo thời gian. Khi Ice Burst trúng kẻ địch, Tấn Công của Resonator sẽ tăng {0} trong {1} giây, tối đa {2} lần.</t>
+          <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt; Có thể tự động nhận được Sự Thanh Khiết theo thời gian. Khi Ice Burst trúng kẻ địch, ATK của Resonator sẽ tăng {0} trong {1} giây, tối đa {2} lần.</t>
         </is>
       </c>
     </row>
@@ -11269,8 +11269,8 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Resonance Liberation]&lt;/color&gt; Băng hà tạo ra từ Resonance Liberation: Ánh Mắt Băng Giá sẽ kích nổ trực tiếp và tăng cường 3 đòn Basic Attack tiếp theo, tạo thêm một Ice Prism Giá. Điều này làm tăng Crit. DMG thêm {0} trong {1} giây, có thể chồng chất lên đến {2} lần.
-Basic Attack 4 có thể kích nổ Ice Thorn, Ice Prism và Glacier trong phạm vi tấn công một lần.</t>
+          <t>&lt;color=#c49e55&gt;[Resonance Liberation]&lt;/color&gt; Băng hà tạo ra từ Resonance Liberation: Ánh Mắt Băng Giá sẽ kích nổ trực tiếp và tăng cường 3 đòn Basic Attack tiếp theo, tạo thêm một Lăng Kính Băng Giá. Điều này làm tăng Crit. DMG thêm {0} trong {1} giây, có thể chồng chất lên đến {2} lần.
+Basic Attack 4 có thể kích nổ Gai Băng, Lăng Kính Băng và Băng Hà trong phạm vi tấn công một lần.</t>
         </is>
       </c>
     </row>
@@ -11335,7 +11335,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt; Sử dụng Resonance Skill sẽ tăng cường Basic Attack. Sát thương Bùng Nổ Băng tăng đáng kể.</t>
+          <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt; Sử dụng Resonance Skill sẽ tăng cường Basic Attack. DMG Bùng Nổ Băng tăng đáng kể.</t>
         </is>
       </c>
     </row>
@@ -11400,7 +11400,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Basic Attack]&lt;/color&gt; Basic Attack 5 tạo thêm một Ice Thorn. Sát thương Vụ Nổ Băng tăng mạnh.</t>
+          <t>&lt;color=#c49e55&gt;[Basic Attack]&lt;/color&gt; Basic Attack 5 tạo thêm một Gai Băng. DMG Vụ Nổ Băng tăng mạnh.</t>
         </is>
       </c>
     </row>
@@ -11465,7 +11465,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Heavy Attack]&lt;/color&gt; Sử dụng Heavy Attack: Bùng Nổ sẽ tăng cường Basic Attack. Sát Thương Vụ Nổ Băng tăng đáng kể.</t>
+          <t>&lt;color=#c49e55&gt;[Heavy Attack]&lt;/color&gt; Sử dụng Heavy Attack: Detonate enhances Basic Attack. Ice Burst DMG is significantly increased.</t>
         </is>
       </c>
     </row>
@@ -11530,7 +11530,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt; Có thể tự động nhận được Sự Thanh Khiết. Khi Ice Burst trúng kẻ địch, Tấn Công của Resonator sẽ tăng nhẹ.</t>
+          <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt; Có thể tự động nhận được Sự Thanh Khiết. Khi Ice Burst trúng kẻ địch, ATK của Resonator sẽ tăng nhẹ.</t>
         </is>
       </c>
     </row>
@@ -11660,7 +11660,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>Mở khóa thêm Chuỗi Resonance của Resonator.</t>
+          <t>Mở khóa thêm Resonance Chain của Resonator.</t>
         </is>
       </c>
     </row>
@@ -11725,7 +11725,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>Mở khóa thêm &lt;color=#3cea36&gt;2&lt;/color&gt; nút trên Chuỗi Resonance của Resonator. Có thể mở khóa tối đa 6 nút.</t>
+          <t>Mở khóa thêm &lt;color=#3cea36&gt;2&lt;/color&gt; nút trên Resonance Chain của Resonator. Có thể mở khóa tối đa 6 nút.</t>
         </is>
       </c>
     </row>
@@ -11922,7 +11922,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>Restore HP khi đánh bại kẻ địch.</t>
+          <t>Hồi phục HP khi đánh bại kẻ địch.</t>
         </is>
       </c>
     </row>
@@ -12052,7 +12052,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>Mỗi &lt;color=#3cea36&gt;5&lt;/color&gt; giây, triệu hồi một tia sét gây sát thương bằng &lt;color=#3cea36&gt;650%&lt;/color&gt; Tấn Công của Resonator khi trúng mục tiêu.</t>
+          <t>Mỗi &lt;color=#3cea36&gt;5&lt;/color&gt; giây, triệu hồi một tia sét gây DMG bằng &lt;color=#3cea36&gt;650%&lt;/color&gt; ATK của Resonator khi trúng mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -12117,7 +12117,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>Giảm Phòng Ngự và nhận thêm Dream Fragments.</t>
+          <t>Giảm Phòng Ngự và nhận thêm Mảnh Giấc Mơ.</t>
         </is>
       </c>
     </row>
@@ -12182,7 +12182,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>Increase Sát Thương Resonance Skill. Sử dụng Resonance Skill sẽ tiêu hao STA.</t>
+          <t>Tăng Sát Thương Resonance Skill. Sử dụng Resonance Skill sẽ tiêu hao STA.</t>
         </is>
       </c>
     </row>
@@ -12247,7 +12247,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>Increase Thêm Sát Thương Resonance Skill lên &lt;color=#3cea36&gt;200%&lt;/color&gt;. Sử dụng Resonance Skill sẽ tiêu hao thêm &lt;color=#ff5454&gt;80&lt;/color&gt; STA.</t>
+          <t>Tăng Thêm Sát Thương Resonance Skill lên &lt;color=#3cea36&gt;200%&lt;/color&gt;. Sử dụng Resonance Skill sẽ tiêu hao thêm &lt;color=#ff5454&gt;80&lt;/color&gt; STA.</t>
         </is>
       </c>
     </row>
@@ -12312,7 +12312,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>Kích hoạt Spark</t>
+          <t>Kích Hoạt Lấp Lánh</t>
         </is>
       </c>
     </row>
@@ -12442,7 +12442,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>Increase Sát Thương gây ra thêm &lt;color=#3cea36&gt;70%&lt;/color&gt; khi bước vào Khu Vực Ký Ức mới, hiệu ứng sẽ mất đi khi nhận sát thương.</t>
+          <t>Tăng Sát Thương gây ra thêm &lt;color=#3cea36&gt;70%&lt;/color&gt; khi bước vào Khu Vực Ký Ức mới, hiệu ứng sẽ mất đi khi nhận DMG.</t>
         </is>
       </c>
     </row>
@@ -12637,7 +12637,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>Gây DMG mạnh mẽ</t>
+          <t>Kẻ gây sát thương cực mạnh</t>
         </is>
       </c>
     </row>
@@ -12702,7 +12702,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>Hồi năng lượng Concerto nhanh</t>
+          <t>Tăng tốc hồi năng lượng concerto</t>
         </is>
       </c>
     </row>
@@ -12832,7 +12832,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>Gây Sát Thương Heavy Attack cao hơn</t>
+          <t>Gây Sát Thương Đòn Tấn Công Mạnh cao hơn</t>
         </is>
       </c>
     </row>
@@ -13352,7 +13352,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>Tăng cường Havoc DMG cho một Resonator cụ thể trong đội</t>
+          <t>Tăng cường Sát Thương Havoc cho một Resonator cụ thể trong đội</t>
         </is>
       </c>
     </row>
@@ -13417,7 +13417,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>Tăng cường Aero DMG cho một Resonator cụ thể trong đội</t>
+          <t>Tăng cường Sát Thương Aero cho một Resonator cụ thể trong đội</t>
         </is>
       </c>
     </row>
@@ -13482,7 +13482,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>Tăng cường Electro DMG cho một Resonator cụ thể trong đội</t>
+          <t>Tăng cường Sát Thương Electro cho một Resonator cụ thể trong đội</t>
         </is>
       </c>
     </row>
@@ -13547,7 +13547,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>Tăng cường Fusion DMG cho một Resonator cụ thể trong đội</t>
+          <t>Tăng cường Sát Thương Fusion cho một Resonator cụ thể trong đội</t>
         </is>
       </c>
     </row>
@@ -13612,7 +13612,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>Tăng cường Glacio DMG cho một Resonator cụ thể trong đội</t>
+          <t>Tăng cường Sát Thương Glacio cho một Resonator cụ thể trong đội</t>
         </is>
       </c>
     </row>
@@ -13677,7 +13677,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>Tăng cường Spectro DMG cho một Resonator cụ thể trong đội</t>
+          <t>Tăng cường Sát Thương Spectro cho một Resonator cụ thể trong đội</t>
         </is>
       </c>
     </row>
@@ -13807,7 +13807,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>Tăng cường Sát Thương Heavy Attack cho một Resonator cụ thể trong đội</t>
+          <t>Tăng cường Sát Thương Đòn Heavy Attack cho một Resonator cụ thể trong đội</t>
         </is>
       </c>
     </row>
@@ -14002,7 +14002,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>Khi Cấp Độ Giao Hưởng đạt B trở lên, sát thương nhận vào giảm 30%.</t>
+          <t>Khi Cấp Độ Giao Hưởng đạt B trở lên, DMG nhận vào giảm 30%.</t>
         </is>
       </c>
     </row>
@@ -14132,7 +14132,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>Tốc độ giảm cấp Symphony Rank giảm 50%, và Tấn Công của Resonator tăng 50%.</t>
+          <t>Tốc độ giảm cấp Symphony Rank giảm 50%, và ATK của Resonator tăng 50%.</t>
         </is>
       </c>
     </row>
@@ -14392,7 +14392,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>Sát thương gây ra của kẻ địch tăng 50%, và hiệu suất tăng hạng Symphony tăng 20%.</t>
+          <t>DMG gây ra của kẻ địch tăng 50%, và hiệu suất tăng hạng Symphony tăng 20%.</t>
         </is>
       </c>
     </row>
@@ -14457,7 +14457,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>Khi Cấp Độ Giao Hưởng đạt B trở lên, sát thương nhận vào giảm 30%.</t>
+          <t>Khi Cấp Độ Giao Hưởng đạt B trở lên, DMG nhận vào giảm 30%.</t>
         </is>
       </c>
     </row>
@@ -14587,7 +14587,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>Tốc độ giảm cấp Symphony Rank giảm 50%, và Tấn Công của Resonator tăng 20%.</t>
+          <t>Tốc độ giảm cấp Symphony Rank giảm 50%, và ATK của Resonator tăng 20%.</t>
         </is>
       </c>
     </row>
@@ -14717,7 +14717,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>DEF giảm 50%.</t>
+          <t>Phòng Ngự giảm 50%.</t>
         </is>
       </c>
     </row>
@@ -14782,7 +14782,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>HP tối đa được đặt về 100. Khi đạt Cấp Giao Hưởng SS, Resonators không thể bị hạ gục.</t>
+          <t>HP tối đa được đặt về 100. Khi đạt Cấp Giao Hưởng SS, Resonator không thể bị hạ gục.</t>
         </is>
       </c>
     </row>
@@ -14847,7 +14847,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>Sát thương gây ra bởi kẻ địch tăng thêm 50%.</t>
+          <t>DMG gây ra bởi kẻ địch tăng thêm 50%.</t>
         </is>
       </c>
     </row>
@@ -14977,7 +14977,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>Dodge thành công sẽ giảm 2 giây Cooldown chiêu của Resonance Skill và Resonance Liberation.</t>
+          <t>Né thành công sẽ giảm 2 giây Thời gian hồi chiêu của Resonance Skill và Resonance Liberation.</t>
         </is>
       </c>
     </row>
@@ -15042,7 +15042,7 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>Dodge thành công sẽ hồi phục 5% HP tối đa. Có thể kích hoạt 1 lần mỗi 3 giây.</t>
+          <t>Né thành công sẽ hồi phục 5% HP tối đa. Có thể kích hoạt 1 lần mỗi 3 giây.</t>
         </is>
       </c>
     </row>
@@ -15107,7 +15107,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>Increase Crit. DMG thêm 40% trong Độ Sâu Ảo Tưởng.</t>
+          <t>Tăng Crit. DMG thêm 40% trong Độ Sâu Ảo Tưởng.</t>
         </is>
       </c>
     </row>
@@ -15172,7 +15172,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>Increase Sát Thương gây ra thêm 35% trong Depths of Illusive Realm.</t>
+          <t>Tăng Sát Thương gây ra thêm 35% trong Depths of Illusive Realm.</t>
         </is>
       </c>
     </row>
@@ -15237,7 +15237,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>Tiêu Hao Dream Fragments để đặt lại Ẩn Dụ một lần.</t>
+          <t>Tiêu Hao Mảnh Giấc Mơ để đặt lại Ẩn Dụ một lần.</t>
         </is>
       </c>
     </row>
@@ -15432,7 +15432,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>Increase HP thêm 35% trong Depths of Illusive Realm.</t>
+          <t>Tăng HP thêm 35% trong Depths of Illusive Realm.</t>
         </is>
       </c>
     </row>
@@ -15497,7 +15497,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>Increase Phòng Ngự thêm 80% trong Depths of Illusive Realm.</t>
+          <t>Tăng Phòng Ngự thêm 80% trong Depths of Illusive Realm.</t>
         </is>
       </c>
     </row>
@@ -15562,7 +15562,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>Giảm 20% sát thương nhận vào tại Vực Ảo Ảnh.</t>
+          <t>Giảm 20% DMG nhận vào tại Vực Ảo Ảnh.</t>
         </is>
       </c>
     </row>
@@ -15627,7 +15627,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>Mỗi giây ở hạng A trở lên, tăng 10% sát thương gây ra trong 2 giây, tối đa 10 tầng.</t>
+          <t>Mỗi giây ở hạng A trở lên, tăng 10% DMG gây ra trong 2 giây, tối đa 10 tầng.</t>
         </is>
       </c>
     </row>
@@ -15824,7 +15824,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt; Khi ở trạng thái Incarnation, Crit. DMG và hiệu ứng hút của Stage 4 Kỹ Năng Basic được tăng cường đáng kể.</t>
+          <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt; Khi ở trạng thái Hóa Thân, Crit. DMG và hiệu ứng hút của Giai Đoạn 4 Kỹ Năng Cơ Bản được tăng cường đáng kể.</t>
         </is>
       </c>
     </row>
@@ -15889,7 +15889,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Basic Attack]&lt;/color&gt; Basic Attack giờ bắt đầu từ Stage 3, tăng đáng kể sát thương và có hiệu ứng đặc biệt.</t>
+          <t>&lt;color=#c49e55&gt;[Basic Attack]&lt;/color&gt; Basic Attack giờ bắt đầu từ Giai Đoạn 3, tăng đáng kể DMG và có hiệu ứng đặc biệt.</t>
         </is>
       </c>
     </row>
@@ -15954,7 +15954,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Basic Attack]&lt;/color&gt; &lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt; Khi ở trạng thái Incarnation, thi triển Basic Attack và Resonance Skill sẽ hồi phục Đồng Hồ Năng Lượng và tăng nhẹ Attack của Resonator.</t>
+          <t>&lt;color=#c49e55&gt;[Basic Attack]&lt;/color&gt; &lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt; Khi ở trạng thái Hóa Thân, thi triển Basic Attack và Resonance Skill sẽ hồi phục Đồng Hồ Năng Lượng và tăng nhẹ ATK của Resonator.</t>
         </is>
       </c>
     </row>
@@ -16019,7 +16019,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Dodge]&lt;/color&gt; Dodge thành công sẽ phục hồi Thanh Forte và kích hoạt Loong's Reign, tăng đáng kể Tấn Công Bổ Sung Spectro.</t>
+          <t>&lt;color=#c49e55&gt;[Né Tránh]&lt;/color&gt; Né tránh thành công sẽ phục hồi Thanh Forte và kích hoạt Loong's Reign, tăng đáng kể Tấn Công Bổ Sung Spectro.</t>
         </is>
       </c>
     </row>
@@ -16149,7 +16149,7 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt; Khi ở trạng thái Incarnation, Crit. DMG tăng thêm {0}, và hiệu ứng hút của Stage 4 Kỹ Năng Basic trong Incarnation được tăng cường đáng kể.</t>
+          <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt; Khi ở trạng thái Hóa Thân, Crit. DMG tăng thêm {0}, và hiệu ứng hút của Giai Đoạn 4 Kỹ Năng Cơ Bản trong Hóa Thân được tăng cường đáng kể.</t>
         </is>
       </c>
     </row>
@@ -16214,7 +16214,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Basic Attack]&lt;/color&gt; Basic Attack giờ bắt đầu từ Stage 3, tăng Hệ Số Sát Thương thêm {0}. Hiệu ứng hút của Basic Attack 3 và phạm vi của Basic Attack 4 được tăng mạnh. Basic Attack 4 giờ gây sát thương {1} lần và hồi thêm {2} Thanh Forte khi gây sát thương.</t>
+          <t>&lt;color=#c49e55&gt;[Basic Attack]&lt;/color&gt; Basic Attack giờ bắt đầu từ Giai Đoạn 3, tăng Hệ Số Sát Thương thêm {0}. Hiệu ứng hút của Basic Attack 3 và phạm vi của Basic Attack 4 được tăng mạnh. Basic Attack 4 giờ gây DMG {1} lần và hồi thêm {2} Thanh Forte khi gây DMG.</t>
         </is>
       </c>
     </row>
@@ -16279,7 +16279,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>Trong trạng thái Incarnation, mỗi đòn &lt;color=#c49e55&gt;[Basic Attack]&lt;/color&gt; hoặc &lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt; sẽ hồi {0} Thanh Forte và tăng Attack của Resonator thêm {1} trong {2} giây, tối đa cộng dồn {3} lần.</t>
+          <t>Trong trạng thái Hóa Thân, mỗi đòn &lt;color=#c49e55&gt;[Basic Attack]&lt;/color&gt; hoặc &lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt; sẽ hồi {0} Thanh Forte và tăng ATK của Resonator thêm {1} trong {2} giây, tối đa cộng dồn {3} lần.</t>
         </is>
       </c>
     </row>
@@ -16347,8 +16347,8 @@
       <c r="M244" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt; Quyền Trị của Loong nay được tăng cường: 
-- Quyền Trị của Loong được kích hoạt khi thi triển Resonance Liberation, tạo ra Vùng Trì Trệ và ban cho Jinhsi {0} Spectro DMG Bonus trong {1} giây. Hiệu ứng này chỉ có thể kích hoạt mỗi {2} giây một lần. 
-- Khi Quyền Trị của Loong đang hoạt động, mỗi {3} giây sẽ giáng sấm sét xuống mục tiêu trong khu vực, gây Spectro DMG bằng {4} Attack của Jinhsi. Khi Quyền Trị của Loong kết thúc, gây Spectro DMG bằng Hệ Số Sát Thương của Incarnation: Kỹ Năng Basic 4, sau đó tấn công khu vực xung quanh với Spectro DMG bằng {5} Attack của Jinhsi.</t>
+- Quyền Trị của Loong được kích hoạt khi thi triển Resonance Liberation, tạo ra Vùng Trì Trệ và ban cho Jinhsi {0} Tăng Sát Thương Spectro trong {1} giây. Hiệu ứng này chỉ có thể kích hoạt mỗi {2} giây một lần. 
+- Khi Quyền Trị của Loong đang hoạt động, mỗi {3} giây sẽ giáng sấm sét xuống mục tiêu trong khu vực, gây Sát Thương Spectro bằng {4} ATK của Jinhsi. Khi Quyền Trị của Loong kết thúc, gây Sát Thương Spectro bằng Hệ Số Sát Thương của Hóa Thân: Kỹ Năng Cơ Bản 4, sau đó tấn công khu vực xung quanh với Sát Thương Spectro bằng {5} ATK của Jinhsi.</t>
         </is>
       </c>
     </row>
@@ -16413,7 +16413,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt; Khi sử dụng kỹ năng làm đầy Thanh Forte, True Sight: Capture sẽ được kích hoạt một lần. Immune sát thương khi thi triển True Sight: Capture, Conquest và Charge.</t>
+          <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt; Khi sử dụng kỹ năng làm đầy Thanh Forte, True Sight: Capture sẽ được kích hoạt một lần. Miễn nhiễm sát thương khi thi triển True Sight: Capture, Conquest và Charge.</t>
         </is>
       </c>
     </row>
@@ -16478,7 +16478,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Heavy Attack]&lt;/color&gt; Fusion DMG tăng nhẹ khi nhận Đồng Điệu. Hiệu ứng này có thể chồng chất và sẽ bị loại bỏ sau khi sử dụng Heavy Attack: Hy Sinh Lửa.</t>
+          <t>&lt;color=#c49e55&gt;[Heavy Attack]&lt;/color&gt; Sát Thương Fusion tăng nhẹ khi nhận Đồng Điệu. Hiệu ứng này có thể chồng chất và sẽ bị loại bỏ sau khi sử dụng Heavy Attack: Hy Sinh Lửa.</t>
         </is>
       </c>
     </row>
@@ -16543,7 +16543,7 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Heavy Attack]&lt;/color&gt; Basic Attack được tăng cường sau khi sử dụng Heavy Attack: Hy Sinh Lửa.</t>
+          <t>&lt;color=#c49e55&gt;[Heavy Attack]&lt;/color&gt; Đòn Basic Attack được tăng cường sau khi sử dụng Heavy Attack: Hy Sinh Lửa.</t>
         </is>
       </c>
     </row>
@@ -16608,8 +16608,8 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Mid-air Attack]&lt;/color&gt; 
-Khi ở trên không, sát thương gây ra tăng nhẹ. Hiệu ứng này có thể cộng dồn.</t>
+          <t>&lt;color=#c49e55&gt;[Tấn Công Giữa Không]&lt;/color&gt; 
+Khi ở trên không, DMG gây ra tăng nhẹ. Hiệu ứng này có thể cộng dồn.</t>
         </is>
       </c>
     </row>
@@ -16674,7 +16674,7 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt; Khi Thanh Forte đầy, đòn tấn công cuối của Resonance Skill sẽ gây thêm sát thương bằng với sát thương của Resonance Liberation.</t>
+          <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt; Khi Thanh Forte đầy, đòn tấn công cuối của Resonance Skill sẽ gây thêm DMG bằng với DMG của Resonance Liberation.</t>
         </is>
       </c>
     </row>
@@ -16739,7 +16739,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt; Khi sử dụng kỹ năng tạo trạng thái Bừng Cháy, gây thêm sát thương bằng với sát thương của 3 giai đoạn đầu của True Sight: Capture. Immune sát thương khi thi triển True Sight: Capture, Conquest và Charge.</t>
+          <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt; Khi sử dụng kỹ năng tạo trạng thái Bừng Cháy, gây thêm DMG bằng với DMG của 3 giai đoạn đầu của True Sight: Capture. Miễn nhiễm DMG khi thi triển True Sight: Capture, Conquest và Charge.</t>
         </is>
       </c>
     </row>
@@ -16804,7 +16804,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Heavy Attack]&lt;/color&gt; Khi nhận trạng thái Enflamement, Fusion DMG tăng thêm {0} trong {1} giây, tối đa {2} lần cộng dồn. Sử dụng Heavy Attack: Flaming Sacrifice sẽ tiêu hao toàn bộ cộng dồn.</t>
+          <t>&lt;color=#c49e55&gt;[Đòn Heavy Attack]&lt;/color&gt; Khi nhận trạng thái Enflamement, DMG Fusion tăng thêm {0} trong {1} giây, tối đa {2} lần cộng dồn. Sử dụng Đòn Heavy Attack: Flaming Sacrifice sẽ tiêu hao toàn bộ cộng dồn.</t>
         </is>
       </c>
     </row>
@@ -16869,7 +16869,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Heavy Attack]&lt;/color&gt; Trong vòng {0} giây sau khi sử dụng Heavy Attack: Flaming Sacrifice, Basic Attack gây thêm sát thương bằng 3 giai đoạn cuối của Basic Attack: True Sight - Conquest. Hiệu ứng này có thể kích hoạt mỗi {2} giây, tối đa {1} lần.</t>
+          <t>&lt;color=#c49e55&gt;[Đòn Heavy Attack]&lt;/color&gt; Trong vòng {0} giây sau khi sử dụng Đòn Heavy Attack: Flaming Sacrifice, Đòn Basic Attack gây thêm DMG bằng 3 giai đoạn cuối của Đòn Basic Attack: True Sight - Conquest. Hiệu ứng này có thể kích hoạt mỗi {2} giây, tối đa {1} lần.</t>
         </is>
       </c>
     </row>
@@ -16934,8 +16934,8 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Mid-air Attack]&lt;/color&gt; 
-Khi ở trên không, sát thương gây ra tăng thêm {0} trong {1} giây, có thể cộng dồn tối đa {2} lần.</t>
+          <t>&lt;color=#c49e55&gt;[Tấn Công Giữa Không]&lt;/color&gt; 
+Khi ở trên không, DMG gây ra tăng thêm {0} trong {1} giây, có thể cộng dồn tối đa {2} lần.</t>
         </is>
       </c>
     </row>
@@ -17000,7 +17000,7 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt; Khi có 4 tầng Bừng Cháy, đòn tấn công cuối của Resonance Skill: True Sight - Capture sẽ gây thêm sát thương bằng với sát thương của Resonance Liberation: Radiance of Fealty khi trúng mục tiêu. Hiệu ứng này có thể kích hoạt mỗi {0} giây một lần.</t>
+          <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt; Khi có 4 tầng Bừng Cháy, đòn tấn công cuối của Resonance Skill: True Sight - Capture sẽ gây thêm DMG bằng với DMG của Resonance Liberation: Radiance of Fealty khi trúng mục tiêu. Hiệu ứng này có thể kích hoạt mỗi {0} giây một lần.</t>
         </is>
       </c>
     </row>
@@ -17065,7 +17065,7 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>Biến thành Hoartoise trong 4 giây, mỗi giây gây 1125.00% Glacio DMG và tung hứng kẻ địch xung quanh. Hồi chiêu: 12 giây.</t>
+          <t>Biến hình thành Hoartoise trong 4 giây, mỗi giây gây 1125.00% Sát Thương Glacio và tung hứng kẻ địch xung quanh. Thời gian hồi: 12 giây.</t>
         </is>
       </c>
     </row>
@@ -17195,7 +17195,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>Khi Resonators trang bị Hoartoise kết thúc bằng Outro Skill, Cooldown chiêu của Kỹ Năng Echo sẽ được đặt lại.</t>
+          <t>Khi Resonator trang bị Hoartoise kết thúc bằng Kỹ Năng Outro, Thời gian hồi chiêu của Kỹ Năng Echo sẽ được đặt lại.</t>
         </is>
       </c>
     </row>
@@ -17260,7 +17260,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>Summon Glacio Prism trong 6 giây để tấn công kẻ địch. Mỗi đòn gây 538,00% Glacio DMG, tăng thêm 66,67% nếu mục tiêu bị Đóng Băng. Hồi chiêu: 10,8 giây.</t>
+          <t>Triệu hồi Lăng Kính Glacio trong 6 giây để tấn công kẻ địch. Mỗi đòn gây 538,00% Sát Thương Glacio, tăng thêm 66,67% nếu mục tiêu bị Đóng Băng. Thời gian hồi: 10,8 giây.</t>
         </is>
       </c>
     </row>
@@ -17455,7 +17455,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>Biến thành Autopuppet Scout để đóng băng kẻ địch xung quanh trong 3 giây, gây 1135.00% Glacio DMG. Cooldown chiêu: 7.2 giây.</t>
+          <t>Biến hình thành Autopuppet Scout để đóng băng kẻ địch xung quanh trong 3 giây, gây 1135.00% Sát Thương Glacio. Thời gian hồi chiêu: 7.2 giây.</t>
         </is>
       </c>
     </row>
@@ -17520,7 +17520,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>Kẻ địch bị đóng băng sẽ gây ít hơn 50% sát thương trong 6 giây sau khi hiệu ứng Đông Cứng kết thúc.</t>
+          <t>Kẻ địch bị đóng băng sẽ gây ít hơn 50% DMG trong 6 giây sau khi hiệu ứng Đông Cứng kết thúc.</t>
         </is>
       </c>
     </row>
@@ -17585,7 +17585,7 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>Increase thời gian Đông cứng thêm 3 giây.</t>
+          <t>Tăng thời gian Đông cứng thêm 3 giây.</t>
         </is>
       </c>
     </row>
@@ -17650,8 +17650,8 @@
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>Summon Tick Tack phát nổ sau một lúc, gây 2220.36% Sát Thương Hỗn Loạn.
-Hồi chiêu: 6 giây.</t>
+          <t>Triệu hồi Tick Tack phát nổ sau một lúc, gây 2220.36% Sát Thương Hỗn Loạn.
+Thời gian hồi: 6 giây.</t>
         </is>
       </c>
     </row>
@@ -17716,7 +17716,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>DMG nổ tăng gấp đôi.</t>
+          <t>Tăng gấp đôi DMG nổ.</t>
         </is>
       </c>
     </row>
@@ -17781,7 +17781,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>Làm mới Cooldown chiêu khi Tick Tack đánh bại kẻ địch bằng vụ nổ của nó.</t>
+          <t>Làm mới thời gian hồi chiêu khi Tick Tack đánh bại kẻ địch bằng vụ nổ của nó.</t>
         </is>
       </c>
     </row>
@@ -17846,7 +17846,7 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>Biến thành Rocksteady Guardian, gây 2526.00% Spectro DMG và tung kẻ địch lên không. Nếu Rocksteady Guardian trúng Glacio Prism, kẻ địch xung quanh sẽ bị Đông Cứng ngay lập tức trong 3 giây. Hồi chiêu: 12 giây.</t>
+          <t>Biến hình thành Rocksteady Guardian, gây 2526.00% Sát Thương Spectro và tung kẻ địch lên không. Nếu Rocksteady Guardian trúng Glacio Prism, kẻ địch xung quanh sẽ bị Đông Cứng ngay lập tức trong 3 giây. Thời gian hồi: 12 giây.</t>
         </is>
       </c>
     </row>
@@ -17911,7 +17911,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>Nhận thêm một lượt sử dụng. Mỗi khi Resonator này hoặc đồng đội sử dụng Kỹ Năng Echo, giảm 33.33% Cooldown chiêu của Rocksteady Guardian.</t>
+          <t>Nhận thêm một lượt sử dụng. Mỗi khi Resonator này hoặc đồng đội sử dụng Kỹ Năng Echo, giảm 33.33% Thời gian hồi chiêu của Rocksteady Guardian.</t>
         </is>
       </c>
     </row>
@@ -17976,7 +17976,7 @@
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>Expand phạm vi sát thương thêm 40%.</t>
+          <t>Mở rộng phạm vi DMG thêm 40%.</t>
         </is>
       </c>
     </row>
@@ -18041,7 +18041,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>Summon Whiff Whaff hút kẻ địch xung quanh vào trung tâm trong 5 giây, gây 149.75% Aero DMG 12 lần. Hồi chiêu: 9.6 giây.</t>
+          <t>Triệu hồi Whiff Whaff hút kẻ địch xung quanh vào trung tâm trong 5 giây, gây 149.75% Sát Thương Aero 12 lần. Thời gian hồi: 9.6 giây.</t>
         </is>
       </c>
     </row>
@@ -18106,7 +18106,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>Kẻ địch bị kéo vào sẽ chịu thêm 60.00% sát thương.</t>
+          <t>Kẻ địch bị kéo vào sẽ chịu thêm 60.00% DMG.</t>
         </is>
       </c>
     </row>
@@ -18172,8 +18172,8 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>Summon Nhạc Công Trống trong 7 giây, liên tục phát ra những nốt nhạc. Đồng đội nhặt nốt nhạc sẽ hồi 10 Concerto Energy và tăng Movement Speed 30% trong 5 giây.
-Hồi chiêu: 12 giây.</t>
+          <t>Triệu hồi Nhạc Công Trống trong 7 giây, liên tục phát ra những nốt nhạc. Đồng đội nhặt nốt nhạc sẽ hồi 10 Năng Lượng Giao Hưởng và tăng Tốc Độ Di Chuyển 30% trong 5 giây.
+Thời gian hồi: 12 giây.</t>
         </is>
       </c>
     </row>
@@ -18238,7 +18238,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>Increase tốc độ di chuyển thêm 30% khi nhặt nốt nhạc.</t>
+          <t>Tăng tốc độ di chuyển thêm 30% khi nhặt nốt nhạc.</t>
         </is>
       </c>
     </row>
@@ -18368,7 +18368,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>Biến thành Feilian Beringal và đập mạnh xuống đất, gây 1140.00% Aero DMG và để lại một cột trụ trong 9 giây. Cột trụ giải phóng sóng xung kích mỗi 3 giây, gây 432.00% Aero DMG. Hồi chiêu: 14 giây.</t>
+          <t>Biến hình thành Feilian Beringal và đập mạnh xuống đất, gây 1140.00% Sát Thương Aero và để lại một cột trụ trong 9 giây. Cột trụ giải phóng sóng xung kích mỗi 3 giây, gây 432.00% Sát Thương Aero. Thời gian hồi: 14 giây.</t>
         </is>
       </c>
     </row>
@@ -18498,7 +18498,7 @@
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>Biến thành Impermanence Heron, phun lửa xuống dưới gây 1470.60% Sát Thương Hệ Havoc và tạo ra một vùng lửa cháy trong 5 giây. Kẻ địch trong vùng chịu 655.20% Sát Thương Hệ Havoc mỗi giây và bị giảm 40% Movement Speed. Hồi chiêu: 10.8 giây.</t>
+          <t>Biến hình thành Impermanence Heron, phun lửa xuống dưới gây 1470.60% Sát Thương Hệ Havoc và tạo ra một vùng lửa cháy trong 5 giây. Kẻ địch trong vùng chịu 655.20% Sát Thương Hệ Havoc mỗi giây và bị giảm 40% Tốc Độ Di Chuyển. Thời gian hồi: 10.8 giây.</t>
         </is>
       </c>
     </row>
@@ -18563,7 +18563,7 @@
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>Increase hiệu ứng giảm Movement Speed của vùng lửa cháy thêm 40%.</t>
+          <t>Tăng hiệu ứng giảm Tốc Độ Di Chuyển của vùng lửa cháy thêm 40%.</t>
         </is>
       </c>
     </row>
@@ -18628,7 +18628,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>Khi rời khỏi vùng thiêu đốt, kẻ địch tiếp tục chịu sát thương và tốc độ di chuyển bị giảm trong 3 giây.</t>
+          <t>Khi rời khỏi vùng thiêu đốt, kẻ địch tiếp tục chịu DMG và tốc độ di chuyển bị giảm trong 3 giây.</t>
         </is>
       </c>
     </row>
@@ -18693,7 +18693,7 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>Giảm nhẹ Thời gian Hồi chiêu của kỹ năng Echo... (10%)</t>
+          <t>Giảm nhẹ Thời gian hồi của kỹ năng Echo... (10%)</t>
         </is>
       </c>
     </row>
@@ -18758,7 +18758,7 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>Giảm đáng kể Cooldown chiêu của kỹ năng Echo! (vẫn là 10%)</t>
+          <t>Giảm đáng kể Thời gian hồi chiêu của kỹ năng Echo! (vẫn là 10%)</t>
         </is>
       </c>
     </row>
@@ -18823,7 +18823,7 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>Recover in: {0}</t>
+          <t>Hồi phục sau: {0}</t>
         </is>
       </c>
     </row>
@@ -18888,7 +18888,7 @@
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>Increase Tấn Công thêm 30% trong Vực Ảo Ảnh.</t>
+          <t>Tăng ATK thêm 30% trong Vực Ảo Ảnh.</t>
         </is>
       </c>
     </row>
@@ -18953,7 +18953,7 @@
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>Increase Crit. Rate thêm 20% trong Độ Sâu Ảo Tưởng: Carnival Trong Giấc Mộng. Phần Crit. Rate vượt mức sẽ chuyển thành Crit. DMG theo tỷ lệ 1:1.</t>
+          <t>Tăng Crit. Rate thêm 20% trong Độ Sâu Ảo Tưởng: Lễ Hội Trong Giấc Mộng. Phần Crit. Rate vượt mức sẽ chuyển thành Crit. DMG theo tỷ lệ 1:1.</t>
         </is>
       </c>
     </row>
@@ -19668,7 +19668,7 @@
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>Kích hoạt 3 Resonance Beacon</t>
+          <t>Kích hoạt 3 Điểm Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -19734,7 +19734,7 @@
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>Trong &lt;color=#fcf585&gt;Tiêu Chuẩn Weapon Triệu Tập&lt;/color&gt;, bạn có thể chọn một &lt;color=#fcf585&gt;5-Star Weapon&lt;/color&gt; làm mục tiêu Triệu Hồi.
+          <t>Trong &lt;color=#fcf585&gt;Triệu Hồi Vũ Khí Tiêu Chuẩn&lt;/color&gt;, bạn có thể chọn một &lt;color=#fcf585&gt;Vũ Khí 5 Sao&lt;/color&gt; làm mục tiêu Triệu Hồi.
 Sau khi chọn, bạn có thể thay đổi bất cứ lúc nào mà không ảnh hưởng đến tính toán Đảm Bảo.</t>
         </is>
       </c>
@@ -19801,7 +19801,7 @@
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>Trong &lt;color=#fcf585&gt;Beginner's Choice Triệu Tập&lt;/color&gt;, bạn có thể chọn một &lt;color=#fcf585&gt;5-Star Resonator&lt;/color&gt; làm mục tiêu Triệu Hồi.
+          <t>Trong &lt;color=#fcf585&gt;Triệu Hồi Lựa Chọn Người Mới&lt;/color&gt;, bạn có thể chọn một &lt;color=#fcf585&gt;Resonator 5 Sao&lt;/color&gt; làm mục tiêu Triệu Hồi.
 Sau khi chọn, bạn có thể thay đổi bất cứ lúc nào mà không ảnh hưởng đến tính toán Đảm Bảo.</t>
         </is>
       </c>
@@ -19868,7 +19868,7 @@
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>Trong &lt;color=#fcf585&gt;Anniversary Weapon Triệu Tập&lt;/color&gt;, bạn có thể chọn một &lt;color=#fcf585&gt;5-Star Weapon&lt;/color&gt; làm mục tiêu Triệu Hồi.
+          <t>Trong &lt;color=#fcf585&gt;Triệu Hồi Vũ Khí Kỷ Niệm&lt;/color&gt;, bạn có thể chọn một &lt;color=#fcf585&gt;Vũ Khí 5 Sao&lt;/color&gt; làm mục tiêu Triệu Hồi.
 Bạn có thể thay đổi lựa chọn bất cứ lúc nào mà không ảnh hưởng đến số lần Đảm Bảo.</t>
         </is>
       </c>
@@ -19935,7 +19935,7 @@
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>Trong &lt;color=#fcf585&gt;Anniversary Resonator Triệu Tập&lt;/color&gt;, bạn có thể chọn một &lt;color=#fcf585&gt;5-Star Resonator&lt;/color&gt; làm mục tiêu Triệu Hồi.
+          <t>Trong &lt;color=#fcf585&gt;Triệu Hồi Resonator Kỷ Niệm&lt;/color&gt;, bạn có thể chọn một &lt;color=#fcf585&gt;Resonator 5 Sao&lt;/color&gt; làm mục tiêu Triệu Hồi.
 Bạn có thể thay đổi lựa chọn bất cứ lúc nào mà không ảnh hưởng đến số lần Đảm Bảo.</t>
         </is>
       </c>
@@ -20002,7 +20002,7 @@
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>Trong &lt;color=#fcf585&gt;New Voyage Resonator Triệu Tập&lt;/color&gt;, bạn có thể chọn một &lt;color=#fcf585&gt;5-Star Resonator&lt;/color&gt; làm mục tiêu Triệu Hồi.
+          <t>Trong &lt;color=#fcf585&gt;Triệu Hồi Resonator Hành Trình Mới&lt;/color&gt;, bạn có thể chọn một &lt;color=#fcf585&gt;Resonator 5 Sao&lt;/color&gt; làm mục tiêu Triệu Hồi.
 Bạn có thể thay đổi lựa chọn bất cứ lúc nào mà không ảnh hưởng đến số lần Đảm Bảo.</t>
         </is>
       </c>
@@ -20069,7 +20069,7 @@
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>Trong &lt;color=#fcf585&gt;New Voyage Weapon Triệu Tập&lt;/color&gt;, bạn có thể chọn một &lt;color=#fcf585&gt;5-Star Weapon&lt;/color&gt; làm mục tiêu Triệu Hồi.
+          <t>Trong &lt;color=#fcf585&gt;Triệu Hồi Vũ Khí Hành Trình Mới&lt;/color&gt;, bạn có thể chọn một &lt;color=#fcf585&gt;Vũ Khí 5 Sao&lt;/color&gt; làm mục tiêu Triệu Hồi.
 Bạn có thể thay đổi lựa chọn bất cứ lúc nào mà không ảnh hưởng đến số lần Đảm Bảo.</t>
         </is>
       </c>
@@ -20135,7 +20135,7 @@
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt; Phục hồi thêm "Sẵn Sàng" khi gây Sát Thương. Khi ở trạng thái "Thấm Đẫm Sấm Sét", nhận thêm {0} Electro DMG Bonus.</t>
+          <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt; Phục hồi thêm "Sẵn Sàng" khi gây Sát Thương. Khi ở trạng thái "Thấm Đẫm Sấm Sét", nhận thêm {0} Tăng Sát Thương Electro.</t>
         </is>
       </c>
     </row>
@@ -20200,7 +20200,7 @@
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt; Khi ở trạng thái "Nhiễm Điện", Đòn Trọng và Dodge Counter sẽ được thay thế bằng "Thác Sấm", gây sát thương bằng {0} sát thương của Basic Attack Stage 5 Nhiễm Điện, và thêm sát thương bằng {1} sát thương của Năng Lượng Resonance.</t>
+          <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt; Khi ở trạng thái "Nhiễm Điện", Đòn Trọng và Dodge Counter Tránh sẽ được thay thế bằng "Thác Sấm", gây DMG bằng {0} DMG của Đòn Cơ Bản Giai Đoạn 5 Nhiễm Điện, và thêm DMG bằng {1} DMG của Năng Lượng Cộng Hưởng.</t>
         </is>
       </c>
     </row>
@@ -20265,7 +20265,7 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt; Đòn Phối Hợp từ "Nêm Sấm" phục hồi thêm "Sẵn Sàng". Khi "Sẵn Sàng" đầy, có thể kích nổ "Nêm Sấm" bằng cách nhấn nút Resonance Skill, gây thêm sát thương bằng {0} Tấn Công của Yuanwu, hút kẻ địch vào và tạo lá chắn bằng {1} Phòng Ngự của Yuanwu trong {2} giây.</t>
+          <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt; Đòn Phối Hợp từ "Nêm Sấm" phục hồi thêm "Sẵn Sàng". Khi "Sẵn Sàng" đầy, có thể kích nổ "Nêm Sấm" bằng cách nhấn nút Resonance Skill, gây thêm DMG bằng {0} ATK của Yuanwu, hút kẻ địch vào và tạo lá chắn bằng {1} Phòng Ngự của Yuanwu trong {2} giây.</t>
         </is>
       </c>
     </row>
@@ -20330,7 +20330,7 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Resonance Liberation]&lt;/color&gt; Nhận thêm {0} Tăng Sát Thương Resonance Liberation. Khi kích hoạt Resonance Liberation, mỗi {1} điểm khiên kích hoạt sẽ tăng thêm {2} sát thương cho lần Resonance Liberation đó.</t>
+          <t>&lt;color=#c49e55&gt;[Resonance Liberation]&lt;/color&gt; Nhận thêm {0} Tăng Sát Thương Resonance Liberation. Khi kích hoạt Resonance Liberation, mỗi {1} điểm khiên kích hoạt sẽ tăng thêm {2} DMG cho lần Resonance Liberation đó.</t>
         </is>
       </c>
     </row>
@@ -20395,7 +20395,7 @@
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Basic Attack]&lt;/color&gt; Resonance Skill sẽ tăng cường cho tối đa 3 đòn Basic Attack tiếp theo. Khi ở trạng thái "Thấm Đẫm Sét", Phòng Ngự tăng thêm {0} Attack của Yuanwu.</t>
+          <t>&lt;color=#c49e55&gt;[Basic Attack]&lt;/color&gt; Resonance Skill sẽ tăng cường cho tối đa 3 đòn Basic Attack tiếp theo. Khi ở trạng thái "Thấm Đẫm Sét", Phòng Ngự tăng thêm {0} ATK của Yuanwu.</t>
         </is>
       </c>
     </row>
@@ -20460,7 +20460,7 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt; Gây Sát Thương sẽ hồi phục thêm Forte Gauge. Khi ở trạng thái "Thấm Điện", nhận thêm phần thưởng Electro DMG đáng kể.</t>
+          <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt; Gây Sát Thương sẽ hồi phục thêm Forte Gauge. Khi ở trạng thái "Thấm Điện", nhận thêm phần thưởng Sát Thương Electro đáng kể.</t>
         </is>
       </c>
     </row>
@@ -20525,7 +20525,7 @@
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt; Khi ở trạng thái "Nhiễm Điện", Đòn Trọng và Dodge Counter gây thêm sát thương.</t>
+          <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt; Khi ở trạng thái "Nhiễm Điện", Đòn Trọng và Dodge Counter Tránh gây thêm sát thương.</t>
         </is>
       </c>
     </row>
@@ -20655,7 +20655,7 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Resonance Liberation]&lt;/color&gt; Increase sát thương Resonance Liberation tương ứng với lượng khiên kích hoạt.</t>
+          <t>&lt;color=#c49e55&gt;[Resonance Liberation]&lt;/color&gt; Tăng DMG Resonance Liberation tương ứng với lượng khiên kích hoạt.</t>
         </is>
       </c>
     </row>
@@ -20785,7 +20785,7 @@
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Heavy Attack]&lt;/color&gt; Nhận thêm {0} Sát Thương Heavy Attack. Sử dụng Resonance Liberation sẽ hồi đầy "Ruby Blossom" và tăng cường đòn "Heavy Attack: Cắt Đôi Hỗn Loạn" tiếp theo để hồi thêm {1} HP tối đa của Danjin.</t>
+          <t>&lt;color=#c49e55&gt;[Heavy Attack]&lt;/color&gt; Nhận thêm {0} Sát Thương Heavy Attack. Sử dụng Resonance Liberation sẽ hồi đầy "Hoa Hồng Đá" và tăng cường đòn "Heavy Attack: Cắt Đôi Hỗn Loạn" tiếp theo để hồi thêm {1} HP tối đa của Danjin.</t>
         </is>
       </c>
     </row>
@@ -20850,7 +20850,7 @@
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt; Kích hoạt Resonance Skill tăng Hồi Phục cho "Hoa Hồng Đỏ". Dodge Counter được thay thế bằng "Heavy Attack: Cắt Hỗn Loạn". "Heavy Attack: Hoa Tán Loạn" gây thêm sát thương bằng {0} sát thương của Resonance Liberation: Vụ Nổ Đỏ Thẫm. Danjin cũng nhận được lá chắn dựa trên {1} HP tối đa của cô trong {2} giây. Hiệu ứng lá chắn chỉ kích hoạt mỗi {3} giây một lần.</t>
+          <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt; Kích hoạt Resonance Skill tăng Hồi Phục cho "Hoa Hồng Đỏ". Dodge Counter Tránh được thay thế bằng "Đòn Nặng: Cắt Hỗn Loạn". "Đòn Nặng: Hoa Tán Loạn" gây thêm DMG bằng {0} DMG của Resonance Liberation: Vụ Nổ Đỏ Thẫm. Danjin cũng nhận được lá chắn dựa trên {1} HP tối đa của cô trong {2} giây. Hiệu ứng lá chắn chỉ kích hoạt mỗi {3} giây một lần.</t>
         </is>
       </c>
     </row>
@@ -20915,7 +20915,7 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt; Nhận thêm {0} Sát Thương Resonance Skill cộng thêm. Tấn Công của Danjin tăng {2} cho mỗi {1} HP đã mất.</t>
+          <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt; Nhận thêm {0} Sát Thương Resonance Skill cộng thêm. ATK của Danjin tăng {2} cho mỗi {1} HP đã mất.</t>
         </is>
       </c>
     </row>
@@ -20980,7 +20980,7 @@
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt; Nhận thêm {0} Havoc DMG cộng thêm. Danjin có thể sử dụng Resonance Skill: "Xung Huyết" bằng cách nhấn lại nút Resonance Skill ngay sau khi dùng Resonance Skill: "Ánh Hồng Đỏ Thẫm". Khi kích hoạt giai đoạn 3 của Resonance Skill: "Xung Huyết", cô nhận được lá chắn dựa trên {1} HP tối đa trong {2} giây. Hiệu ứng lá chắn chỉ kích hoạt {4} lần mỗi {3} giây.</t>
+          <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt; Nhận thêm {0} Sát Thương Havoc cộng thêm. Danjin có thể sử dụng Resonance Skill: "Xung Huyết" bằng cách nhấn lại nút Resonance Skill ngay sau khi dùng Resonance Skill: "Ánh Hồng Đỏ Thẫm". Khi kích hoạt giai đoạn 3 của Resonance Skill: "Xung Huyết", cô nhận được lá chắn dựa trên {1} HP tối đa trong {2} giây. Hiệu ứng lá chắn chỉ kích hoạt {4} lần mỗi {3} giây.</t>
         </is>
       </c>
     </row>
@@ -21045,7 +21045,7 @@
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt; "Incinerating Will" sẽ giảm thêm Havoc RES của mục tiêu đi {0} trong {1} giây. Khi sử dụng Resonance Skill: "Erosion Đỏ Thẫm" giai đoạn 2, Danjin sẽ nhận được một lớp khiên dựa trên {2} HP tối đa của cô trong {3} giây. Hiệu ứng khiên này có thể kích hoạt tối đa {5} lần mỗi {4} giây.</t>
+          <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt; "Ý Chí Thiêu Đốt" sẽ giảm thêm Kháng Havoc của mục tiêu đi {0} trong {1} giây. Khi sử dụng Resonance Skill: "Xói Mòn Đỏ Thẫm" giai đoạn 2, Danjin sẽ nhận được một lớp khiên dựa trên {2} HP tối đa của cô trong {3} giây. Hiệu ứng khiên này có thể kích hoạt tối đa {5} lần mỗi {4} giây.</t>
         </is>
       </c>
     </row>
@@ -21175,7 +21175,7 @@
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt;&lt;color=#c49e55&gt;[Heavy Attack]&lt;/color&gt; Kích hoạt Resonance Skill sẽ tăng tốc độ hồi Fort Gauge. Đòn Dodge Counter được thay thế bằng Heavy Attack: "Chém Hỗn Loạn". Heavy Attack: "Hoa Tán Loạn" gây thêm sát thương và tạo khiên cho Danjin.</t>
+          <t>&lt;color=#c49e55&gt;[Resonance Skill] &lt;/color&gt;&lt;color=#c49e55&gt;[Đòn Tấn Công Mạnh]&lt;/color&gt; Kích hoạt Resonance Skill sẽ tăng tốc độ hồi Fort Gauge. Đòn Phản Đòn Dodge được thay thế bằng Đòn Tấn Công Mạnh: "Chém Hỗn Loạn". Đòn Tấn Công Mạnh: "Hoa Tán Loạn" gây thêm DMG và tạo khiên cho Danjin.</t>
         </is>
       </c>
     </row>
@@ -21240,7 +21240,7 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt; Nhận thêm lượng lớn Sát Thương Resonance Skill cộng thêm. Tấn Công của Danjin tăng dựa trên lượng HP đã mất.</t>
+          <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt; Nhận thêm lượng lớn Sát Thương Resonance Skill cộng thêm. ATK của Danjin tăng dựa trên lượng HP đã mất.</t>
         </is>
       </c>
     </row>
@@ -21305,7 +21305,7 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt; Nhận thêm lượng lớn Havoc DMG cộng thêm. Danjin có thể sử dụng Resonance Skill: "Xung Huyết" ngay sau khi dùng Resonance Skill: "Ánh Hồng Đỏ Thẫm". Cô nhận được lá chắn khi kích hoạt giai đoạn 3 của Resonance Skill: "Xung Huyết".</t>
+          <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt; Nhận thêm lượng lớn Sát Thương Havoc cộng thêm. Danjin có thể sử dụng Resonance Skill: "Xung Huyết" ngay sau khi dùng Resonance Skill: "Ánh Hồng Đỏ Thẫm". Cô nhận được lá chắn khi kích hoạt giai đoạn 3 của Resonance Skill: "Xung Huyết".</t>
         </is>
       </c>
     </row>
@@ -21370,7 +21370,7 @@
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;Resonance Skill&lt;/color&gt; "Incinerating Will" giảm mạnh Havoc RES của mục tiêu. Danjin nhận khiên khi sử dụng Resonance Skill: Giai đoạn 2 "Erosion Đỏ Rực".</t>
+          <t>&lt;color=#c49e55&gt;Resonance Skill&lt;/color&gt; "Ý Chí Thiêu Đốt" giảm mạnh Kháng Havoc của mục tiêu. Danjin nhận khiên khi sử dụng Resonance Skill: Giai đoạn 2 "Xói Mòn Đỏ Rực".</t>
         </is>
       </c>
     </row>
@@ -21500,7 +21500,7 @@
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t>[Hòa Tấu Carnival] The Dreamless gia tăng Sát Thương Kỹ Năng của Companions Hòa Tấu.</t>
+          <t>[Hòa Tấu Carnival] The Dreamless gia tăng Sát Thương Kỹ Năng của Đồng Hành Hòa Tấu.</t>
         </is>
       </c>
     </row>
@@ -21565,7 +21565,7 @@
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>Restore 100 điểm Concerto Energy và bước vào trạng thái "Bóp Méo" trong {0} giây sau khi sử dụng Kỹ Năng Echo. Trong trạng thái "Bóp Méo", hồi phục &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; {Cus:Sap,S=điểm P=điểm Concerto Energy SapTag=1} mỗi giây và kích hoạt "Điệp Khúc", gây sát thương bằng {2} Tấn Công của Resonator mỗi khi trúng đòn từ kỹ năng Đồng Hành Giao Hưởng. Kỹ Năng Echo sẽ sẵn sàng để sử dụng lại trong {3} giây sau khi "Bóp Méo" kết thúc. Khi sử dụng, nó kích hoạt "Bản Hợp Xướng", biến bạn thành Dreamless để tung đòn kết liễu và vô hiệu hóa mọi sát thương nhận vào khi thi triển. Mỗi lần "Điệp Khúc" kích hoạt sẽ tăng sát thương của "Bản Hợp Xướng" tiếp theo lên {4}, cộng dồn tối đa {5} lần.</t>
+          <t>Hồi phục 100 điểm Năng Lượng Giao Hưởng và bước vào trạng thái "Bóp Méo" trong {0} giây sau khi sử dụng Kỹ Năng Echo. Trong trạng thái "Bóp Méo", hồi phục &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; {Cus:Sap,S=điểm P=điểm Năng Lượng Giao Hưởng SapTag=1} mỗi giây và kích hoạt "Điệp Khúc", gây DMG bằng {2} ATK của Resonator mỗi khi trúng đòn từ kỹ năng Đồng Hành Giao Hưởng. Kỹ Năng Echo sẽ sẵn sàng để sử dụng lại trong {3} giây sau khi "Bóp Méo" kết thúc. Khi sử dụng, nó kích hoạt "Bản Hợp Xướng", biến bạn thành Dreamless để tung đòn kết liễu và vô hiệu hóa mọi DMG nhận vào khi thi triển. Mỗi lần "Điệp Khúc" kích hoạt sẽ tăng DMG của "Bản Hợp Xướng" tiếp theo lên {4}, cộng dồn tối đa {5} lần.</t>
         </is>
       </c>
     </row>
@@ -21630,7 +21630,7 @@
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>"Chorale" có thể kích hoạt khi không ở trạng thái "Distortion". Khi ở trạng thái "Distortion", hệ số sát thương của "Chorale" tăng lên {0}.</t>
+          <t>"Chorale" có thể kích hoạt khi không ở trạng thái "Distortion". Khi ở trạng thái "Distortion", hệ số DMG của "Chorale" tăng lên {0}.</t>
         </is>
       </c>
     </row>
@@ -21695,7 +21695,7 @@
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>Khi ở trạng thái "Bóp Méo", "Loạt Đòn" sẽ gây thêm {0} sát thương mỗi khi "Thánh Ca" được kích hoạt.</t>
+          <t>Khi ở trạng thái "Bóp Méo", "Loạt Đòn" sẽ gây thêm {0} DMG mỗi khi "Thánh Ca" được kích hoạt.</t>
         </is>
       </c>
     </row>
@@ -21760,7 +21760,7 @@
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>Kích hoạt Kỹ Năng Echo để bước vào "Distortion", liên tục hồi phục Concerto Energy và kích hoạt "Chorale" gây thêm sát thương cho mỗi kỹ năng Đồng Hành Concerto được kích hoạt. Kích hoạt một Kỹ Năng another Echo ngay sau khi "Distortion" kết thúc để tung ra "Volley" kết liễu đối thủ.</t>
+          <t>Kích hoạt Kỹ Năng Tiếng Vọng để bước vào "Distortion", liên tục hồi phục Concerto Energy và kích hoạt "Chorale" gây thêm DMG cho mỗi kỹ năng Đồng Hành Concerto được kích hoạt. Kích hoạt một Kỹ Năng Tiếng Vọng khác ngay sau khi "Distortion" kết thúc để tung ra "Volley" kết liễu đối thủ.</t>
         </is>
       </c>
     </row>
@@ -21825,7 +21825,7 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>"Chorale" có thể kích hoạt khi không ở trạng thái "Distortion" và gây sát thương tăng lên khi ở trạng thái "Distortion."</t>
+          <t>"Chorale" có thể kích hoạt khi không ở trạng thái "Distortion" và gây DMG tăng lên khi ở trạng thái "Distortion."</t>
         </is>
       </c>
     </row>
@@ -21890,7 +21890,7 @@
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t>Khi ở trạng thái "Bóp Méo", "Loạt Đòn" sẽ gây thêm sát thương mỗi khi "Thánh Ca" được kích hoạt.</t>
+          <t>Khi ở trạng thái "Bóp Méo", "Loạt Đòn" sẽ gây thêm DMG mỗi khi "Thánh Ca" được kích hoạt.</t>
         </is>
       </c>
     </row>
@@ -21960,8 +21960,8 @@
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Liberation]&lt;/color&gt; Resonance Liberation được tăng cường:
 - Mỗi lần Basic Attack: Xoay Người - Đâm Gây Sát Thương, nhận {0} Khối Siêu Hình. Hiệu ứng này có thể kích hoạt mỗi {1} giây.
-- Kích hoạt Resonance Liberation sẽ hồi đầy Năng Lực Performance và cho phép Xiangli Yao giữ tối đa {2} Khối Siêu Hình.
-- Kích hoạt Resonance Skill: Luật Lệnh sẽ tăng Attack của Xiangli Yao lên {3} trong {4} giây.</t>
+- Kích hoạt Resonance Liberation sẽ hồi đầy Năng Lực Biểu Diễn và cho phép Xiangli Yao giữ tối đa {2} Khối Siêu Hình.
+- Kích hoạt Resonance Skill: Luật Lệnh sẽ tăng ATK của Xiangli Yao lên {3} trong {4} giây.</t>
         </is>
       </c>
     </row>
@@ -22030,7 +22030,7 @@
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Liberation]&lt;/color&gt; Resonance Liberation được tăng cường:
 - Khi gây Sát Thương bằng Basic Attack, hồi {0} Resonance Energy thêm. Hiệu ứng này có thể kích hoạt mỗi {1} giây.
-- Kích hoạt Resonance Liberation sẽ nhận thêm {2} Khối Siêu Hình và cho phép Xiangli Yao giữ tối đa {3} Khối Siêu Hình. Khi ở trạng thái Resonance Liberation: Trực Giác, nhận thêm {4} Electro DMG Bonus.</t>
+- Kích hoạt Resonance Liberation sẽ nhận thêm {2} Khối Siêu Hình và cho phép Xiangli Yao giữ tối đa {3} Khối Siêu Hình. Khi ở trạng thái Resonance Liberation: Trực Giác, nhận thêm {4} Tăng Sát Thương Electro.</t>
         </is>
       </c>
     </row>
@@ -22095,7 +22095,7 @@
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Basic Attack]&lt;/color&gt; Nhận {0} thưởng Electro DMG. Mỗi khi Basic Attack gây sát thương, hồi {1} Năng Lượng. Hiệu ứng này chỉ kích hoạt mỗi {2} giây một lần. Kích hoạt Resonance Skill: Giải Mã ở trạng thái Năng Lượng tối đa sẽ hồi {3} Resonance Energy và giảm {4} giây Cooldown chiêu của Resonance Liberation.</t>
+          <t>&lt;color=#c49e55&gt;[Basic Attack]&lt;/color&gt; Nhận {0} thưởng Sát Thương Electro. Mỗi khi Basic Attack gây DMG, hồi {1} Năng Lượng. Hiệu ứng này chỉ kích hoạt mỗi {2} giây một lần. Kích hoạt Resonance Skill: Giải Mã ở trạng thái Năng Lượng tối đa sẽ hồi {3} Resonance Energy và giảm {4} giây thời gian hồi chiêu của Resonance Liberation.</t>
         </is>
       </c>
     </row>
@@ -22225,7 +22225,7 @@
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Resonance Liberation]&lt;/color&gt; Khi ở trạng thái Resonance Liberation, khả năng chống gián đoạn của Xiangli Yao được tăng cường và Tấn Công của cậu tăng {0}.</t>
+          <t>&lt;color=#c49e55&gt;[Resonance Liberation]&lt;/color&gt; Khi ở trạng thái Resonance Liberation, khả năng chống gián đoạn của Xiangli Yao được tăng cường và ATK của cậu tăng {0}.</t>
         </is>
       </c>
     </row>
@@ -22290,7 +22290,7 @@
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Resonance Liberation]&lt;/color&gt; Kích hoạt Resonance Liberation hồi phục Thanh Nhạc. Basic Attack tạo Siêu Lập Phương và tăng số lượng tối đa của Siêu Lập Phương. Khi ở trạng thái Resonance Liberation, kích hoạt Resonance Skill ở Thanh Nhạc đầy sẽ tăng mạnh Attack của Tương Ly Yao.</t>
+          <t>&lt;color=#c49e55&gt;[Resonance Liberation]&lt;/color&gt; Kích hoạt Resonance Liberation hồi phục Thanh Nhạc. Đòn Basic Attack tạo Siêu Lập Phương và tăng số lượng tối đa của Siêu Lập Phương. Khi ở trạng thái Resonance Liberation, kích hoạt Resonance Skill ở Thanh Nhạc đầy sẽ tăng mạnh ATK của Tương Ly Dao.</t>
         </is>
       </c>
     </row>
@@ -22355,7 +22355,7 @@
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Resonance Liberation]&lt;/color&gt; Kích hoạt Resonance Liberation tạo thêm Siêu Lập Phương và tăng số lượng tối đa của Siêu Lập Phương. Khi ở trạng thái Resonance Liberation, nhận thêm Electro DMG Bonus đáng kể. Basic Attack hồi phục thêm Resonance Energy.</t>
+          <t>&lt;color=#c49e55&gt;[Resonance Liberation]&lt;/color&gt; Kích hoạt Resonance Liberation tạo thêm Siêu Lập Phương và tăng số lượng tối đa của Siêu Lập Phương. Khi ở trạng thái Resonance Liberation, nhận thêm Tăng Sát Thương Electro đáng kể. Đòn Basic Attack hồi phục thêm Resonance Energy.</t>
         </is>
       </c>
     </row>
@@ -22420,7 +22420,7 @@
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Basic Attack]&lt;/color&gt; Nhận tăng thưởng Electro DMG đáng kể. Basic Attack hồi thêm Năng Lượng Forte và giảm Cooldown chiêu của Resonance Liberation khi không ở trạng thái Resonance Liberation.</t>
+          <t>&lt;color=#c49e55&gt;[Basic Attack]&lt;/color&gt; Nhận tăng thưởng Sát Thương Electro đáng kể. Basic Attack hồi thêm Năng Lượng Forte và giảm thời gian hồi chiêu của Resonance Liberation khi không ở trạng thái Resonance Liberation.</t>
         </is>
       </c>
     </row>
@@ -22550,7 +22550,7 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Resonance Liberation]&lt;/color&gt; Khi ở trạng thái Resonance Liberation, khả năng chống gián đoạn và Tấn Công được tăng cường đáng kể.</t>
+          <t>&lt;color=#c49e55&gt;[Resonance Liberation]&lt;/color&gt; Khi ở trạng thái Resonance Liberation, khả năng chống gián đoạn và ATK được tăng cường đáng kể.</t>
         </is>
       </c>
     </row>
@@ -22615,7 +22615,7 @@
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Resonance Liberation]&lt;/color&gt; Increase sát thương của Linh Hồn Mực Nhỏ thêm {0}, nhưng giảm số lượng tối đa có thể triệu hồi đi {1}.</t>
+          <t>&lt;color=#c49e55&gt;[Resonance Liberation]&lt;/color&gt; Tăng DMG của Linh Hồn Mực Nhỏ thêm {0}, nhưng giảm số lượng tối đa có thể triệu hồi đi {1}.</t>
         </is>
       </c>
     </row>
@@ -22680,7 +22680,7 @@
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt; "Stroke of Genius" hoặc "Đỉnh Cao Sáng Tạo" khi trúng mục tiêu sẽ tạo ra {0} lớp "Dấu Cọ" tồn tại trong {1} giây và có thể tích lũy tối đa {2} lần. Mỗi {3} giây chỉ có thể tạo ra tối đa 1 lớp. Khi Basic Attack, Mid-air Attack hoặc Dodge Counter Gây Sát Thương, tiêu hao {4} lớp để triệu hồi Héraut Ngà, gây sát thương bằng {5} sát thương của "Đỉnh Cao Sáng Tạo". Mỗi {6} giây chỉ có thể triệu hồi 1 Héraut Ngà theo cách này.</t>
+          <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt; "Nét Thiên Tài" hoặc "Đỉnh Cao Sáng Tạo" khi trúng mục tiêu sẽ tạo ra {0} lớp "Dấu Cọ" tồn tại trong {1} giây và có thể tích lũy tối đa {2} lần. Mỗi {3} giây chỉ có thể tạo ra tối đa 1 lớp. Khi Basic Attack, Tấn Công Giữa Không hoặc Dodge Counter Gây Sát Thương, tiêu hao {4} lớp để triệu hồi Héraut Ngà, gây DMG bằng {5} DMG của "Đỉnh Cao Sáng Tạo". Mỗi {6} giây chỉ có thể triệu hồi 1 Héraut Ngà theo cách này.</t>
         </is>
       </c>
     </row>
@@ -22746,7 +22746,7 @@
       <c r="M342" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Normal Attack]&lt;/color&gt; 
-Khi Basic Attack, Mid-air Attack hoặc Phản Công Dodge gây sát thương, giảm Cooldown chiêu của Resonance Liberation {0} giây và nhận thêm {1} Glacio DMG trong {2} giây. Hiệu ứng này có thể cộng dồn tối đa {3} lần và kích hoạt mỗi {4} giây một lần.</t>
+Khi Basic Attack, Tấn Công Giữa Không hoặc Phản Công Né Tránh gây DMG, giảm thời gian hồi chiêu của Resonance Liberation {0} giây và nhận thêm {1} Sát Thương Glacio trong {2} giây. Hiệu ứng này có thể cộng dồn tối đa {3} lần và kích hoạt mỗi {4} giây một lần.</t>
         </is>
       </c>
     </row>
@@ -22813,7 +22813,7 @@
       <c r="M343" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt; Kích hoạt Resonance Skill sẽ tạo {0} tầng "Đường Viền" cho {1} giây, tối đa {2} tầng. Hiệu ứng này chỉ kích hoạt mỗi {3} giây một lần.
-"Đường Viền": Mỗi tầng giúp Zhezhi bỏ qua {4} Glacio RES DMG của mục tiêu khi gây sát thương.</t>
+"Đường Viền": Mỗi tầng giúp Zhezhi bỏ qua {4} Kháng Sát Thương Glacio của mục tiêu khi gây DMG.</t>
         </is>
       </c>
     </row>
@@ -22878,7 +22878,7 @@
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt; Khi Zenith Sáng Tạo gây Sát Thương, triệu hồi tất cả Tinh Linh Mực sẵn có tấn công mục tiêu. Cooldown triệu hồi Tinh Linh Mực giảm đáng kể.</t>
+          <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt; Khi Zenith Sáng Tạo gây Sát Thương, triệu hồi tất cả Tinh Linh Mực sẵn có tấn công mục tiêu. Thời gian hồi triệu hồi Tinh Linh Mực giảm đáng kể.</t>
         </is>
       </c>
     </row>
@@ -22943,7 +22943,7 @@
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Resonance Liberation]&lt;/color&gt; Tăng đáng kể sát thương của Linh Hồn Mực Nhỏ, nhưng giảm số lượng tối đa có thể triệu hồi.</t>
+          <t>&lt;color=#c49e55&gt;[Resonance Liberation]&lt;/color&gt; Tăng đáng kể DMG của Linh Hồn Mực Nhỏ, nhưng giảm số lượng tối đa có thể triệu hồi.</t>
         </is>
       </c>
     </row>
@@ -23073,7 +23073,7 @@
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Basic Attack]&lt;/color&gt; Khi Normal Attack gây sát thương, giảm Cooldown chiêu của Resonance Liberation và nhận thưởng Glacio DMG.</t>
+          <t>&lt;color=#c49e55&gt;[Basic Attack]&lt;/color&gt; Khi Đòn Thường gây DMG, giảm thời gian hồi chiêu của Resonance Liberation và nhận thưởng Sát Thương Glacio.</t>
         </is>
       </c>
     </row>
@@ -23138,7 +23138,7 @@
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt; Kích hoạt Resonance Skill tạo ra "Đường Viền" giúp bỏ qua Glacio RES DMG của mục tiêu.</t>
+          <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt; Kích hoạt Resonance Skill tạo ra "Đường Viền" giúp bỏ qua Kháng Sát Thương Glacio của mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -23203,7 +23203,7 @@
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt; Summon tất cả Tinh Linh Mực sẵn có khi Zenith Sáng Tạo gây Sát Thương.</t>
+          <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt; Triệu hồi tất cả Tinh Linh Mực sẵn có khi Zenith Sáng Tạo gây Sát Thương.</t>
         </is>
       </c>
     </row>
@@ -23333,7 +23333,7 @@
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>Sau khi đánh bại &lt;color=#ff5454&gt;3&lt;/color&gt; kẻ địch bằng Resonance Skill, nhận hiệu ứng sau: Khi sử dụng Resonance Skill, triệu hồi Hypercubes tấn công mục tiêu, gây tổng cộng &lt;color=#3cea36&gt;1000%&lt;/color&gt; sát thương. Hiệu ứng này có thể kích hoạt mỗi 12 giây một lần.</t>
+          <t>Sau khi đánh bại &lt;color=#ff5454&gt;3&lt;/color&gt; kẻ địch bằng Resonance Skill, nhận hiệu ứng sau: Khi sử dụng Resonance Skill, triệu hồi Hypercubes tấn công mục tiêu, gây tổng cộng &lt;color=#3cea36&gt;1000%&lt;/color&gt; DMG. Hiệu ứng này có thể kích hoạt mỗi 12 giây một lần.</t>
         </is>
       </c>
     </row>
@@ -23463,7 +23463,7 @@
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>Sau khi đánh bại &lt;color=#ff5454&gt;3&lt;/color&gt; kẻ địch bằng Resonance Skill, nhận hiệu ứng sau: Khi sử dụng Resonance Skill, triệu hồi Ivory Herald tấn công mục tiêu, gây tổng cộng &lt;color=#3cea36&gt;500%&lt;/color&gt; sát thương. Hiệu ứng này có thể kích hoạt mỗi 6 giây một lần.</t>
+          <t>Sau khi đánh bại &lt;color=#ff5454&gt;3&lt;/color&gt; kẻ địch bằng Resonance Skill, nhận hiệu ứng sau: Khi sử dụng Resonance Skill, triệu hồi Ivory Herald tấn công mục tiêu, gây tổng cộng &lt;color=#3cea36&gt;500%&lt;/color&gt; DMG. Hiệu ứng này có thể kích hoạt mỗi 6 giây một lần.</t>
         </is>
       </c>
     </row>
@@ -23528,7 +23528,7 @@
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t>Tấn Công tăng sau khi tiêu diệt một số lượng nhất định Khu Vực Ký Ức có kẻ địch [Phantasm Partita].</t>
+          <t>ATK tăng sau khi tiêu diệt một số lượng nhất định Khu Vực Ký Ức có kẻ địch [Phantasm Partita].</t>
         </is>
       </c>
     </row>
@@ -23593,7 +23593,7 @@
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t>Tăng &lt;color=#3cea36&gt;40%&lt;/color&gt; Tấn Công sau khi quét sạch &lt;color=#ff5454&gt;2&lt;/color&gt; Khu Vực Ký Ức với kẻ địch &lt;color=#ff5454&gt;[Phantasm Partita]&lt;/color&gt;.</t>
+          <t>Tăng &lt;color=#3cea36&gt;40%&lt;/color&gt; ATK sau khi quét sạch &lt;color=#ff5454&gt;2&lt;/color&gt; Khu Vực Ký Ức với kẻ địch &lt;color=#ff5454&gt;[Phantasm Partita]&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -23658,7 +23658,7 @@
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>Giảm Phòng Ngự trong vài Vùng Ký Ức tiếp theo, sau đó tăng Tấn Công.</t>
+          <t>Giảm Phòng Ngự trong vài Vùng Ký Ức tiếp theo, sau đó tăng ATK.</t>
         </is>
       </c>
     </row>
@@ -23723,7 +23723,7 @@
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>Giảm Phòng Ngự &lt;color=#ff5454&gt;80%&lt;/color&gt; trong &lt;color=#ff5454&gt;3&lt;/color&gt; Vùng Ký Ức tiếp theo. Sau khi vượt qua thành công, hiệu ứng này sẽ biến mất và tăng &lt;color=#3cea36&gt;60%&lt;/color&gt; Tấn Công.</t>
+          <t>Giảm Phòng Ngự &lt;color=#ff5454&gt;80%&lt;/color&gt; trong &lt;color=#ff5454&gt;3&lt;/color&gt; Vùng Ký Ức tiếp theo. Sau khi vượt qua thành công, hiệu ứng này sẽ biến mất và tăng &lt;color=#3cea36&gt;60%&lt;/color&gt; ATK.</t>
         </is>
       </c>
     </row>
@@ -23788,7 +23788,7 @@
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>Sau khi đánh bại một số kẻ địch bằng Basic Attack, thỉnh thoảng sẽ triệu hồi Đòn Phán Xét khi gây sát thương.</t>
+          <t>Sau khi đánh bại một số kẻ địch bằng Đòn Cơ Bản, thỉnh thoảng sẽ triệu hồi Đòn Phán Xét khi gây DMG.</t>
         </is>
       </c>
     </row>
@@ -23853,7 +23853,7 @@
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t>Sau khi đánh bại &lt;color=#ff5454&gt;10&lt;/color&gt; kẻ địch bằng Basic Attack, nhận hiệu ứng sau: Khi gây sát thương, có &lt;color=#3cea36&gt;25%&lt;/color&gt; cơ hội triệu hồi Đòn Phán Xét gây &lt;color=#3cea36&gt;200%&lt;/color&gt; sát thương. Hiệu ứng này có thể kích hoạt mỗi 1.5 giây một lần.</t>
+          <t>Sau khi đánh bại &lt;color=#ff5454&gt;10&lt;/color&gt; kẻ địch bằng Đòn Cơ Bản, nhận hiệu ứng sau: Khi gây DMG, có &lt;color=#3cea36&gt;25%&lt;/color&gt; cơ hội triệu hồi Đòn Phán Xét gây &lt;color=#3cea36&gt;200%&lt;/color&gt; DMG. Hiệu ứng này có thể kích hoạt mỗi 1.5 giây một lần.</t>
         </is>
       </c>
     </row>
@@ -24052,7 +24052,7 @@
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Concerto]&lt;/color&gt; Dodge thành công sẽ hồi phục 100 Concerto Energy. Hiệu ứng này chỉ có thể kích hoạt mỗi 6 giây một lần.</t>
+          <t>&lt;color=#ffd12f&gt;[Concerto]&lt;/color&gt; Né thành công sẽ hồi phục 100 Concerto Energy. Hiệu ứng này chỉ có thể kích hoạt mỗi 6 giây một lần.</t>
         </is>
       </c>
     </row>
@@ -24117,7 +24117,7 @@
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Concerto]&lt;/color&gt; Dodge thành công sẽ hồi phục 100 Concerto Energy.</t>
+          <t>&lt;color=#ffd12f&gt;[Concerto]&lt;/color&gt; Né thành công sẽ hồi phục 100 Concerto Energy.</t>
         </is>
       </c>
     </row>
@@ -24312,7 +24312,7 @@
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>Increase &lt;color=#ffd12f&gt;[Concerto]&lt;/color&gt; DMG của Intro Skill của Concerto Companion thêm 35%.</t>
+          <t>&lt;color=#ffd12f&gt;[Concerto]&lt;/color&gt; Tăng 35% Sát Thương Kỹ Năng Khởi Động của Đồng Đội Concerto.</t>
         </is>
       </c>
     </row>
@@ -24377,7 +24377,7 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Concerto]&lt;/color&gt; Increase Sát Thương Intro Skill của Đồng Đội Concerto.</t>
+          <t>&lt;color=#ffd12f&gt;[Concerto]&lt;/color&gt; Tăng Sát Thương Kỹ Năng Khởi Động của Đồng Đội Concerto.</t>
         </is>
       </c>
     </row>
@@ -24442,7 +24442,7 @@
       </c>
       <c r="M368" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Echo Skill]&lt;/color&gt; Sử dụng Kỹ Năng Echo làm tăng Crit. Rate của tất cả thành viên trong đội thêm 30% trong 5 giây.</t>
+          <t>&lt;color=#ffd12f&gt;[Kỹ Năng Echo]&lt;/color&gt; Sử dụng Kỹ Năng Echo làm tăng Crit. Rate của tất cả thành viên trong đội thêm 30% trong 5 giây.</t>
         </is>
       </c>
     </row>
@@ -24507,7 +24507,7 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Echo Skill]&lt;/color&gt; Sử dụng Kỹ Năng Echo làm tăng Crit. Rate của tất cả thành viên trong đội.</t>
+          <t>&lt;color=#ffd12f&gt;[Kỹ Năng Echo]&lt;/color&gt; Sử dụng Kỹ Năng Echo làm tăng Crit. Rate của tất cả thành viên trong đội.</t>
         </is>
       </c>
     </row>
@@ -24702,7 +24702,7 @@
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Concerto]&lt;/color&gt; Triệu hồi Đồng Hành Concerto giúp giảm 15% sát thương nhận vào trong 5 giây.</t>
+          <t>&lt;color=#ffd12f&gt;[Concerto]&lt;/color&gt; Triệu hồi Đồng Hành Concerto giúp giảm 15% DMG nhận vào trong 5 giây.</t>
         </is>
       </c>
     </row>
@@ -24767,7 +24767,7 @@
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Concerto]&lt;/color&gt; Triệu hồi Đồng Hành Concerto giúp giảm sát thương nhận vào.</t>
+          <t>&lt;color=#ffd12f&gt;[Concerto]&lt;/color&gt; Triệu hồi Đồng Hành Concerto giúp giảm DMG nhận vào.</t>
         </is>
       </c>
     </row>
@@ -24832,7 +24832,7 @@
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Concerto]&lt;/color&gt; Triệu hồi Đồng Hành Concerto sẽ tăng Sát Thương Resonance Skill và giảm Cooldown chiêu 3 giây.</t>
+          <t>&lt;color=#ffd12f&gt;[Concerto]&lt;/color&gt; Triệu hồi Đồng Hành Concerto sẽ tăng Sát Thương Resonance Skill và giảm thời gian hồi chiêu 3 giây.</t>
         </is>
       </c>
     </row>
@@ -24897,7 +24897,7 @@
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;[Concerto]&lt;/color&gt; Triệu hồi Đồng Hành Concerto sẽ tăng Sát Thương Resonance Skill và giảm Cooldown chiêu.</t>
+          <t>&lt;color=#ffd12f&gt;[Concerto]&lt;/color&gt; Triệu hồi Đồng Hành Concerto sẽ tăng Sát Thương Resonance Skill và giảm thời gian hồi chiêu.</t>
         </is>
       </c>
     </row>
@@ -25352,7 +25352,7 @@
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>Đòn Kiếm Bóng Tối gây thêm Sát Thương và Khuếch Đại Sát Thương Status Tiêu Cực tác động lên mục tiêu.</t>
+          <t>Đòn Kiếm Bóng Tối gây thêm Sát Thương và Khuếch Đại Sát Thương Trạng Thái Tiêu Cực tác động lên mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -25417,7 +25417,7 @@
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>Liên tục gây Status Tiêu Cực lên mục tiêu sẽ triệu hồi False Sovereign để thi triển Deluge Judgment.</t>
+          <t>Liên tục gây Trạng Thái Tiêu Cực lên mục tiêu sẽ triệu hồi False Sovereign để thi triển Deluge Judgment.</t>
         </is>
       </c>
     </row>
@@ -25547,7 +25547,7 @@
       </c>
       <c r="M385" t="inlineStr">
         <is>
-          <t>Skill Echo được thay thế bằng "Biến hình thành Crownless". Tấn công trúng mục tiêu sẽ sinh ra "Sức Mạnh Vương Miện". Khi "Sức Mạnh Vương Miện" đạt {0}, Skill Echo tiếp theo sẽ biến bạn thành Crownless. Ở dạng Crownless, bạn mất {1} HP mỗi giây và kết thúc biến hình ngay khi thời gian biến hình kết thúc.</t>
+          <t>Kỹ năng Echo được thay thế bằng "Biến hình thành Crownless". Tấn công trúng mục tiêu sẽ sinh ra "Sức Mạnh Vương Miện". Khi "Sức Mạnh Vương Miện" đạt {0}, Kỹ năng Echo tiếp theo sẽ biến bạn thành Crownless. Ở dạng Crownless, bạn mất {1} HP mỗi giây và kết thúc biến hình ngay khi thời gian biến hình kết thúc.</t>
         </is>
       </c>
     </row>
@@ -25613,7 +25613,7 @@
       </c>
       <c r="M386" t="inlineStr">
         <is>
-          <t>Sau khi sử dụng Kỹ Năng Vang Âm, nhận Kháng Đứt Quãng được tăng cường và Shield tương đương {0} HP tối đa trong {1} giây.
+          <t>Sau khi sử dụng Kỹ Năng Vang Âm, nhận Kháng Đứt Quãng được tăng cường và Khiên tương đương {0} HP tối đa trong {1} giây.
 Khi có khiên, tấn công sẽ hồi phục {2} Resonance Energy khi trúng mục tiêu, kích hoạt mỗi {3} giây một lần.</t>
         </is>
       </c>
@@ -25744,7 +25744,7 @@
       </c>
       <c r="M388" t="inlineStr">
         <is>
-          <t>Tăng đáng kể sát thương Status Tiêu Cực.</t>
+          <t>Tăng đáng kể DMG Trạng Thái Tiêu Cực.</t>
         </is>
       </c>
     </row>
@@ -25809,7 +25809,7 @@
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>Tăng đáng kể Echo DMG.</t>
+          <t>Tăng đáng kể DMG Echo.</t>
         </is>
       </c>
     </row>
@@ -25874,7 +25874,7 @@
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>Tăng Crit. DMG thêm {0}.</t>
+          <t>Tăng Crit. DMG {0}.</t>
         </is>
       </c>
     </row>
@@ -25939,7 +25939,7 @@
       </c>
       <c r="M391" t="inlineStr">
         <is>
-          <t>Tăng Sát thương Status Tiêu cực lên {0}.</t>
+          <t>Tăng DMG Trạng thái Tiêu cực lên {0}.</t>
         </is>
       </c>
     </row>
@@ -26070,7 +26070,7 @@
       </c>
       <c r="M393" t="inlineStr">
         <is>
-          <t>Summon Inferno Rider thực hiện Attack Phối Hợp với Lửa Nóng Chảy vào mục tiêu sau mỗi 5 đòn tấn công liên tiếp. Lửa Nóng Chảy để lại Vùng Đất Cháy sau khi phát nổ.
+          <t>Triệu hồi Inferno Rider thực hiện Tấn Công Phối Hợp với Lửa Nóng Chảy vào mục tiêu sau mỗi 5 đòn tấn công liên tiếp. Lửa Nóng Chảy để lại Vùng Đất Cháy sau khi phát nổ.
 Mỗi giây, kẻ địch trên Vùng Đất Cháy sẽ chịu 1 tầng Bỏng. Vùng Đất Cháy tồn tại trong 4 giây.</t>
         </is>
       </c>
@@ -26201,7 +26201,7 @@
       </c>
       <c r="M395" t="inlineStr">
         <is>
-          <t>Increase HP thêm 45% trong Depths of Illusive Realm.</t>
+          <t>Tăng HP thêm 45% trong Depths of Illusive Realm.</t>
         </is>
       </c>
     </row>
@@ -26266,7 +26266,7 @@
       </c>
       <c r="M396" t="inlineStr">
         <is>
-          <t>Increase Sát Thương gây ra thêm 50% trong Depths of Illusive Realm.</t>
+          <t>Tăng Sát Thương gây ra thêm 50% trong Depths of Illusive Realm.</t>
         </is>
       </c>
     </row>
@@ -26331,7 +26331,7 @@
       </c>
       <c r="M397" t="inlineStr">
         <is>
-          <t>Dodge thành công sẽ tạo ra lá chắn tương đương 50% HP tối đa trong 3 giây. Có thể kích hoạt mỗi 6 giây một lần.</t>
+          <t>Né thành công sẽ tạo ra lá chắn tương đương 50% HP tối đa trong 3 giây. Có thể kích hoạt mỗi 6 giây một lần.</t>
         </is>
       </c>
     </row>
@@ -26396,7 +26396,7 @@
       </c>
       <c r="M398" t="inlineStr">
         <is>
-          <t>Kích hoạt Beacon Cộng hưởng tại Mắt Asteria</t>
+          <t>Kích hoạt Đèn hiệu Cộng hưởng tại Mắt Asteria</t>
         </is>
       </c>
     </row>
@@ -26461,7 +26461,7 @@
       </c>
       <c r="M399" t="inlineStr">
         <is>
-          <t>Biến thành Rocksteady Guardian để gây {0} Spectro DMG và ban cho các thành viên trong đội gần đó một lớp &lt;color=#ffd12f&gt;Shield&lt;/color&gt; dựa trên {1} HP Tối Đa của người sử dụng. Đồng thời tăng khả năng chống gián đoạn cho người sử dụng. Hiệu ứng kéo dài {2} giây. Hồi chiêu: {3} giây.</t>
+          <t>Biến hình thành Rocksteady Guardian để gây {0} Sát Thương Spectro và ban cho các thành viên trong đội gần đó một lớp &lt;color=#ffd12f&gt;Khiên&lt;/color&gt; dựa trên {1} HP Tối Đa của người sử dụng. Đồng thời tăng khả năng chống gián đoạn cho người sử dụng. Hiệu ứng kéo dài {2} giây. Thời gian hồi: {3} giây.</t>
         </is>
       </c>
     </row>
@@ -26526,7 +26526,7 @@
       </c>
       <c r="M400" t="inlineStr">
         <is>
-          <t>Summon Gulpuff tạo ra &lt;color=#ffd12f&gt;healing field&lt;/color&gt;. Tất cả đồng đội trong phạm vi này phục hồi {0} HP cộng thêm lượng HP bằng {1} Tấn Công của người triệu hồi. Resonators trong phạm vi cũng nhận được {2} Giảm Sát Thương. Hiệu ứng kéo dài {3} giây. Hồi chiêu: {4} giây.</t>
+          <t>Triệu hồi Gulpuff tạo ra &lt;color=#ffd12f&gt;trường hồi phục&lt;/color&gt;. Tất cả đồng đội trong phạm vi này phục hồi {0} HP cộng thêm lượng HP bằng {1} ATK của người triệu hồi. Resonator trong phạm vi cũng nhận được {2} Giảm Sát Thương. Hiệu ứng kéo dài {3} giây. Thời gian hồi: {4} giây.</t>
         </is>
       </c>
     </row>
@@ -26591,7 +26591,7 @@
       </c>
       <c r="M401" t="inlineStr">
         <is>
-          <t>Summon Zig Zag tạo ra &lt;color=#ffd12f&gt;invincible field&lt;/color&gt;. Tất cả Resonators trong lĩnh vực này miễn nhiễm mọi sát thương trong {0} giây. Đồng thời, Resonators bị ảnh hưởng còn nhận thêm {1} Crit. Rate và {2} Crit. DMG. Hồi chiêu: {3} giây.</t>
+          <t>Triệu hồi Zig Zag tạo ra &lt;color=#ffd12f&gt;lĩnh vực bất khả xâm phạm&lt;/color&gt;. Tất cả Resonator trong lĩnh vực này miễn nhiễm mọi DMG trong {0} giây. Đồng thời, Resonator bị ảnh hưởng còn nhận thêm {1} Crit. Rate và {2} Crit. DMG. Thời gian hồi: {3} giây.</t>
         </is>
       </c>
     </row>
@@ -26656,7 +26656,7 @@
       </c>
       <c r="M402" t="inlineStr">
         <is>
-          <t>Biến thành Dreamless để gây {0} Havoc DMG và &lt;color=#ffd12f&gt;boost ATK&lt;/color&gt; cho các thành viên trong đội gần đó thêm {1}. Đồng thời hồi phục {2} Concerto Energy mỗi giây và tăng Sát Thương Resonance Skill lên mục tiêu Bất Động thêm {3}. Hiệu ứng kéo dài {4} giây. Hồi chiêu: {5} giây.</t>
+          <t>Biến hình thành Dreamless để gây {0} Sát Thương Havoc và &lt;color=#ffd12f&gt;tăng ATK&lt;/color&gt; cho các thành viên trong đội gần đó thêm {1}. Đồng thời hồi phục {2} Concerto Energy mỗi giây và tăng Sát Thương Resonance Skill lên mục tiêu Bất Động thêm {3}. Hiệu ứng kéo dài {4} giây. Thời gian hồi: {5} giây.</t>
         </is>
       </c>
     </row>
@@ -26721,7 +26721,7 @@
       </c>
       <c r="M403" t="inlineStr">
         <is>
-          <t>Biến thành Feilian Beringal để gây {0} Aero DMG và &lt;color=#ffd12f&gt;boost Resonance Liberation DMG&lt;/color&gt; cho các thành viên trong đội ở gần thêm {1}. Đồng thời tăng Sát Thương Resonance Liberation lên mục tiêu Bất Động thêm {2}. Hiệu ứng kéo dài {3} giây. Trong thời gian này, Feilian Beringal triệu hồi một cột trụ giải phóng sóng xung kích, mỗi đợt gây {4} Aero DMG. Resonators trúng sóng xung kích sẽ nhận được {5} Resonance Energy và giảm {6} Cooldown chiêu Resonance Liberation. Hồi chiêu: {7} giây.</t>
+          <t>Biến hình thành Feilian Beringal để gây {0} Sát Thương Aero và &lt;color=#ffd12f&gt;tăng Sát Thương Resonance Liberation&lt;/color&gt; cho các thành viên trong đội ở gần thêm {1}. Đồng thời tăng Sát Thương Resonance Liberation lên mục tiêu Bất Động thêm {2}. Hiệu ứng kéo dài {3} giây. Trong thời gian này, Feilian Beringal triệu hồi một cột trụ giải phóng sóng xung kích, mỗi đợt gây {4} Sát Thương Aero. Resonator trúng sóng xung kích sẽ nhận được {5} Resonance Energy và giảm {6} Thời gian hồi chiêu Resonance Liberation. Thời gian hồi: {7} giây.</t>
         </is>
       </c>
     </row>
@@ -26786,7 +26786,7 @@
       </c>
       <c r="M404" t="inlineStr">
         <is>
-          <t>Biến thành Hoartoise trong {0} giây, mỗi giây gây tối đa {1} Glacio DMG lên kẻ địch xung quanh và nhận 5 lớp "Cứng Cáp". Mỗi lớp "Cứng Cáp" &lt;color=#ffd12f&gt;reduces incoming DMG&lt;/color&gt; {2} và tăng Movement Speed {3}. Mỗi khi bị tấn công sẽ mất 1 lớp "Cứng Cáp" (tối đa 1 lớp mỗi giây). Đòn tấn công trong trạng thái biến hình sẽ tăng Tấn Công cho đồng đội gần đó {4} khi trúng đích (tối đa 1 lớp mỗi giây), có thể tích lũy tối đa {5} lần, kéo dài {6} giây. Mất hết lớp "Cứng Cáp" sẽ xóa toàn bộ hiệu ứng tăng Tấn Công và kết thúc biến hình. Hồi chiêu: {7} giây.</t>
+          <t>Biến hình thành Hoartoise trong {0} giây, mỗi giây gây tối đa {1} Sát Thương Glacio lên kẻ địch xung quanh và nhận 5 lớp "Cứng Cáp". Mỗi lớp "Cứng Cáp" &lt;color=#ffd12f&gt;giảm DMG nhận vào&lt;/color&gt; {2} và tăng Tốc Độ Di Chuyển {3}. Mỗi khi bị tấn công sẽ mất 1 lớp "Cứng Cáp" (tối đa 1 lớp mỗi giây). Đòn tấn công trong trạng thái biến hình sẽ tăng ATK cho đồng đội gần đó {4} khi trúng đích (tối đa 1 lớp mỗi giây), có thể tích lũy tối đa {5} lần, kéo dài {6} giây. Mất hết lớp "Cứng Cáp" sẽ xóa toàn bộ hiệu ứng tăng ATK và kết thúc biến hình. Thời gian hồi: {7} giây.</t>
         </is>
       </c>
     </row>
@@ -26851,8 +26851,8 @@
       </c>
       <c r="M405" t="inlineStr">
         <is>
-          <t>Summon Nhạc Công Trống trong {0} giây, tạo ra các nốt nhạc. Mỗi nốt nhạc đồng đội nhặt được sẽ &lt;color=#ffd12f&gt;increases ATK by {1}&lt;/color&gt;, hồi {2} HP, tăng Movement Speed {3} và hồi {4} Thể Lực. Ngoài ra, tăng Sát Thương Basic Attack và Heavy Attack lên mục tiêu Bất Động thêm {5}. Hiệu ứng kéo dài {6} giây. Trong suốt trận đấu, Attack của tất cả Resonators sẽ tăng {7} cho mỗi nốt nhạc đã nhặt.
-Hồi chiêu: {8} giây.</t>
+          <t>Triệu hồi Nhạc Công Trống trong {0} giây, tạo ra các nốt nhạc. Mỗi nốt nhạc đồng đội nhặt được sẽ &lt;color=#ffd12f&gt;tăng ATK {1}&lt;/color&gt;, hồi {2} HP, tăng Tốc Độ Di Chuyển {3} và hồi {4} STA. Ngoài ra, tăng Sát Thương Đòn Cơ Bản và Đòn Nặng lên mục tiêu Bất Động thêm {5}. Hiệu ứng kéo dài {6} giây. Trong suốt trận đấu, ATK của tất cả Resonator sẽ tăng {7} cho mỗi nốt nhạc đã nhặt.
+Thời gian hồi: {8} giây.</t>
         </is>
       </c>
     </row>
@@ -26917,7 +26917,7 @@
       </c>
       <c r="M406" t="inlineStr">
         <is>
-          <t>Summon Jué để tạo ra &lt;color=#ffd12f&gt;stagnation field&lt;/color&gt; kéo dài {0} giây. Khi kích hoạt, nó làm tăng Tốc Độ Tiêu Hao Concerto Vibrancy của các Resonator gần đó lên {1}. Kẻ địch trong trường bị giảm {2} Phòng Ngự và {3} Kháng Tất Cả Thuộc Tính. Trong thời gian này, Jué bay lượn trên không và gây {4} Spectro DMG, đồng thời triệu hồi sấm sét giáng xuống kẻ địch gần đó tối đa 5 lần, mỗi lần gây {5} Spectro DMG. Sau đó, Jué xoáy xuống tấn công kẻ địch xung quanh hai lần, mỗi lần gây {6} Spectro DMG. Hồi chiêu: {7} giây.</t>
+          <t>Triệu hồi Jué để tạo ra &lt;color=#ffd12f&gt;trường trì trệ&lt;/color&gt; kéo dài {0} giây. Khi kích hoạt, nó làm tăng Tốc Độ Tiêu Hao Sức Mạnh Rung Động của các Cộng Hưởng Giả gần đó lên {1}. Kẻ địch trong trường bị giảm {2} Phòng Ngự và {3} Kháng Tất Cả Thuộc Tính. Trong thời gian này, Jué bay lượn trên không và gây {4} Sát Thương Spectro, đồng thời triệu hồi sấm sét giáng xuống kẻ địch gần đó tối đa 5 lần, mỗi lần gây {5} Sát Thương Spectro. Sau đó, Jué xoáy xuống tấn công kẻ địch xung quanh hai lần, mỗi lần gây {6} Sát Thương Spectro. Thời gian hồi: {7} giây.</t>
         </is>
       </c>
     </row>
@@ -26982,7 +26982,7 @@
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>Biến thành Tempest Mephis để gây {0} Electro DMG và &lt;color=#ffd12f&gt;reduce the targets' Vibration Strength by {1}&lt;/color&gt;. Nếu mục tiêu bị Hóa Đá từ đòn tấn công này, tăng sát thương nhận vào {2} và giảm Cooldown chiêu Resonance Skill của tất cả Resonators {3} trong {4} giây. Cooldown: {5} giây.</t>
+          <t>Biến thành Tempest Mephis để gây {0} DMG Electro và &lt;color=#ffd12f&gt;giảm Sức Rung của mục tiêu {1}&lt;/color&gt;. Nếu mục tiêu bị Hóa Đá từ đòn tấn công này, tăng DMG nhận vào {2} và giảm Thời gian hồi chiêu Resonance Skill của tất cả Resonator {3} trong {4} giây. Thời gian hồi: {5} giây.</t>
         </is>
       </c>
     </row>
@@ -27047,7 +27047,7 @@
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t>Mục tiêu theo dõi được tìm thấy tại {0}.</t>
+          <t>Đã xác định vị trí mục tiêu tại {0}.</t>
         </is>
       </c>
     </row>
@@ -27309,7 +27309,7 @@
       </c>
       <c r="M412" t="inlineStr">
         <is>
-          <t>Một chiếc mặt nạ băng được tạo ra bởi Forte của Youhu. Thiết kế khác với bản gốc, nhưng nụ cười ranh mãnh trên mặt nạ lại phản chiếu chính Dodget tinh quái của cô khi bày mưu tính kế. 
+          <t>Một chiếc mặt nạ băng được tạo ra bởi Forte của Youhu. Thiết kế khác với bản gốc, nhưng nụ cười ranh mãnh trên mặt nạ lại phản chiếu chính nét tinh quái của cô khi bày mưu tính kế. 
 Youhu thường nghịch chiếc mặt nạ này trong thời gian rảnh, giữ nó như lời nhắc nhở về lần cô suýt bị lừa khi thẩm định món đồ cổ vào đầu sự nghiệp. 
 Ngoài việc là biểu tượng cảnh tỉnh, nó còn là đạo cụ hoàn hảo để dọa người khác hoặc chơi khăm những ai lọt vào tầm ngắm của cô.</t>
         </is>
@@ -27530,7 +27530,7 @@
       </c>
       <c r="M415" t="inlineStr">
         <is>
-          <t>Thử Nghiệm Special Enemies</t>
+          <t>Thử Nghiệm Kẻ Thù Đặc Biệt</t>
         </is>
       </c>
     </row>
@@ -27595,7 +27595,7 @@
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>4. Kẻ địch đặc biệt</t>
+          <t>4. Kẻ Thù Đặc Biệt</t>
         </is>
       </c>
     </row>
@@ -27855,7 +27855,7 @@
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t>Unison Resonance</t>
+          <t>Cộng Hưởng Đồng Nhất</t>
         </is>
       </c>
     </row>
@@ -28135,21 +28135,21 @@
           <t>Nàng tỉnh giấc sau giấc mơ.
 Gió hú dữ dội nơi mép mái nhà khi nàng vươn vai, nheo mắt nhìn xuống những con phố nhộn nhịp bên dưới. Xe cộ ngang dọc trên đường, đèn hậu nối nhau thành một dây lửa rực rỡ. Chống cằm lên tay, nàng bắt đầu ngân nga.
 Đó là bài hát nàng học được từ {PlayerName}.
-Tất nhiên, nàng chưa từng nghe trực tiếp từ {PlayerName} {Male=chính anh ấy;Female=chính cô ấy}, nàng đã lén lút học thuộc.
+Tất nhiên, nàng chưa từng nghe trực tiếp từ {PlayerName} {Male=him;Female=her}, nàng đã lén lút học thuộc.
 Họ có thể không phải kẻ thù, nhưng mối quan hệ giữa họ còn lâu mới thân thiện—tốt lắm cũng chỉ là sự quen biết một chiều. Sự hiện diện của {PlayerName} đã thu hút sự chú ý của nhiều phe phái, kể cả tổ chức của nàng. Nhưng điều đó chẳng mảy may quan trọng với nàng, cũng chẳng phải điều nàng có thể bận tâm.
 Nàng chỉ là một "hạt giống được chọn", một "bông hoa" nở ra với mục đích duy nhất là săn đuổi {PlayerName}. Hầu hết những ngày qua, những mũi tiêm khiến nàng chìm trong sương mù, lơ lửng giữa ranh giới tỉnh thức, chỉ còn lại bản năng khao khát một người nào đó khắc sâu trong tim.
 Chất lỏng được tiêm vào người nàng có mùi hăng nồng, kéo lý trí của nàng vào vũng lầy, cướp đi sự minh mẫn và bản ngã.
 Suy nghĩ của nàng quay cuồng hỗn loạn, như một quả bom sắp nổ, buộc phải thiết lập lại ngay trước khi đếm ngược kết thúc.
 Nhưng nàng chẳng quan tâm.
-Ngoài {PlayerName}, chẳng có gì khác khiến nàng bận lòng. Đôi khi, {Male=anh ấy;Female=cô ấy} chỉ như một bóng hình mờ trên nền vải trắng, một phác họa của kẻ xa lạ. Bức chân dung ấy được vẽ nên từ những mảnh thông tin nàng cật lực thu thập—họ gần gũi đến thế mà chưa từng thực sự gặp mặt. Nàng không biết {Male=anh ấy;Female=cô ấy} trông như thế nào.
+Ngoài {PlayerName}, chẳng có gì khác khiến nàng bận lòng. Đôi khi, {Male=he;Female=she} chỉ như một bóng hình mờ trên nền vải trắng, một phác họa của kẻ xa lạ. Bức chân dung ấy được vẽ nên từ những mảnh thông tin nàng cật lực thu thập—họ gần gũi đến thế mà chưa từng thực sự gặp mặt. Nàng không biết {Male=he;Female=she} trông như thế nào.
 Nghe nói khoảng cách này là cần thiết để tránh bị hệ thống &lt;te href=850110&gt;Tethys&lt;/te&gt; theo dõi. Mọi tiếp xúc đều bị cấm.
 Nhưng nàng khao khát gặp {PlayerName} biết bao!
 Nàng cười khẩy khi ngồi trên mép tòa nhà, nguy hiểm. Những dây leo quấn quanh cánh tay nàng, vươn cao hơn, những nụ hoa mong manh từ từ hé nở ở đầu ngọn.
 Bỗng nhiên, một ý nghĩ lóe lên.
-"Ta sẽ tặng {Male=anh ấy;Female=cô ấy} một bông hoa."
+"Ta sẽ tặng {Male=him;Female=her} một bông hoa."
 Ý nghĩ vừa xuất hiện đã chiếm trọn tâm trí nàng. Nàng mường tượng khoảnh khắc tìm thấy {PlayerName} và trao món quà này—một đóa hoa mọc lên từ chính cơ thể nàng. Nó sẽ không bao giờ héo úa hay tàn lụi, trừ khi nàng chết đi. Nhưng cũng nhanh như khi đến, ý nghĩ ấy lại tan biến vào hỗn loạn trong tâm trí, không để lại dấu vết.
-Nàng không biết rằng, hàng thế kỷ sau, khung cảnh trước mắt nàng sẽ biến mất trong &lt;te href=850075&gt;Lament&lt;/te&gt;. Nàng sẽ lang thang vô tận trong mê cung ký ức cho đến một buổi sáng thu bên hồ ở Làng Petalfall, nơi nàng cuối cùng cũng gặp được {PlayerName}, đến để giải cứu ngôi làng khỏi các cuộc tấn công của Discord. Từ đó, nàng sẽ gia nhập &lt;te href=850109&gt;the Black Shores&lt;/te&gt; và cùng nhau trải qua vài trăm năm trước khi {Male=anh ấy;Female=cô ấy} rời bỏ nàng. Nàng cũng sẽ rời Black Shores, chỉ để tái ngộ hàng thập kỷ sau ở &lt;te href=850091&gt;Jinzhou&lt;/te&gt;. Tất cả những tương lai ấy vẫn chưa diễn ra, như những khả năng đang say ngủ trong hạt giống, chờ đợi vận mệnh nở rộ.
-Nàng nhảy khỏi tòa nhà, những dây leo đan xen qua các công trình trong thành phố, tìm kiếm {Male=anh ấy;Female=cô ấy}.</t>
+Nàng không biết rằng, hàng thế kỷ sau, khung cảnh trước mắt nàng sẽ biến mất trong &lt;te href=850075&gt;Lament&lt;/te&gt;. Nàng sẽ lang thang vô tận trong mê cung ký ức cho đến một buổi sáng thu bên hồ ở Làng Petalfall, nơi nàng cuối cùng cũng gặp được {PlayerName}, đến để giải cứu ngôi làng khỏi các cuộc tấn công của Tacet Discord. Từ đó, nàng sẽ gia nhập &lt;te href=850109&gt;Bờ Biển Đen&lt;/te&gt; và cùng nhau trải qua vài trăm năm trước khi {Male=he;Female=she} rời bỏ nàng. Nàng cũng sẽ rời Bờ Biển Đen, chỉ để tái ngộ hàng thập kỷ sau ở &lt;te href=850091&gt;Jinzhou&lt;/te&gt;. Tất cả những tương lai ấy vẫn chưa diễn ra, như những khả năng đang say ngủ trong hạt giống, chờ đợi vận mệnh nở rộ.
+Nàng nhảy khỏi tòa nhà, những dây leo đan xen qua các công trình trong thành phố, tìm kiếm {Male=him;Female=her}.</t>
         </is>
       </c>
     </row>
@@ -28215,8 +28215,8 @@
       </c>
       <c r="M425" t="inlineStr">
         <is>
-          <t>Để có trải nghiệm tốt nhất, hãy hoàn thành Nhiệm Vụ Chính Chương I Act VIII trước khi đến Rinascita.
-Bạn vẫn có thể đến Rinascita sớm bằng cách mở khóa và chấp nhận Chương II Prologue. Điều này cũng sẽ mở khóa các chức năng Điều Chỉnh Thời Gian và Chuyển Đổi Resonance, cùng một số Tiện Ích, nhưng có thể ảnh hưởng đến trải nghiệm câu chuyện của bạn.</t>
+          <t>Để có trải nghiệm tốt nhất, hãy hoàn thành Nhiệm Vụ Chính Chương I Hồi VIII trước khi đến Rinascita.
+Bạn vẫn có thể đến Rinascita sớm bằng cách mở khóa và chấp nhận Lời Mở Đầu Chương II. Điều này cũng sẽ mở khóa các chức năng Điều Chỉnh Thời Gian và Chuyển Đổi Cộng Hưởng, cùng một số Tiện Ích, nhưng có thể ảnh hưởng đến trải nghiệm câu chuyện của bạn.</t>
         </is>
       </c>
     </row>
@@ -28282,8 +28282,8 @@
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t>Để có trải nghiệm tốt nhất, hãy hoàn thành Nhiệm Vụ Chính Chương II - Đoạn Nối "Starlight Chảy Trong Mống Mắt" trước khi đến Lahai-Roi.
-Bạn vẫn có thể đến Lahai-Roi sớm trong câu chuyện bằng cách mở khóa và chấp nhận Lời Mở Đầu Chương III. Điều này cũng sẽ mở khóa các chức năng Điều Chỉnh Thời Gian và Chuyển Đổi Resonance, cùng một số Tiện Ích, nhưng có thể ảnh hưởng đến trải nghiệm câu chuyện của bạn.</t>
+          <t>Để có trải nghiệm tốt nhất, hãy hoàn thành Nhiệm Vụ Chính Chương II - Đoạn Nối "Ánh Sao Chảy Trong Mống Mắt" trước khi đến Lahai-Roi.
+Bạn vẫn có thể đến Lahai-Roi sớm trong câu chuyện bằng cách mở khóa và chấp nhận Lời Mở Đầu Chương III. Điều này cũng sẽ mở khóa các chức năng Điều Chỉnh Thời Gian và Chuyển Đổi Cộng Hưởng, cùng một số Tiện Ích, nhưng có thể ảnh hưởng đến trải nghiệm câu chuyện của bạn.</t>
         </is>
       </c>
     </row>
@@ -28478,7 +28478,7 @@
       </c>
       <c r="M429" t="inlineStr">
         <is>
-          <t>Đến bờ sông ở Montelli Quarter để tìm Echo mục tiêu</t>
+          <t>Đến bờ sông ở Khu Montelli để tìm Echo mục tiêu</t>
         </is>
       </c>
     </row>
@@ -28673,7 +28673,7 @@
       </c>
       <c r="M432" t="inlineStr">
         <is>
-          <t>Đến con phố ở City Square để tìm Dư Âm mục tiêu</t>
+          <t>Đến con phố ở Quảng Trường Thành Phố để tìm Dư Âm mục tiêu</t>
         </is>
       </c>
     </row>
@@ -28738,7 +28738,7 @@
       </c>
       <c r="M433" t="inlineStr">
         <is>
-          <t>Đến bờ sông ở City Square để tìm Echo mục tiêu</t>
+          <t>Đến bờ sông ở Quảng Trường Thành Phố để tìm Echo mục tiêu</t>
         </is>
       </c>
     </row>
@@ -28803,7 +28803,7 @@
       </c>
       <c r="M434" t="inlineStr">
         <is>
-          <t>Đến chỗ đất cao ở Square Thành phố để tìm Echo mục tiêu</t>
+          <t>Đến chỗ đất cao ở Quảng trường Thành phố để tìm Echo mục tiêu</t>
         </is>
       </c>
     </row>
@@ -28868,7 +28868,7 @@
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t>Đến đài phun nước ở Square Thành phố để tìm Echo mục tiêu</t>
+          <t>Đến đài phun nước ở Quảng trường Thành phố để tìm Echo mục tiêu</t>
         </is>
       </c>
     </row>
@@ -28933,7 +28933,7 @@
       </c>
       <c r="M436" t="inlineStr">
         <is>
-          <t>Đến đài phun nước ở Square Thành phố để tìm Echo mục tiêu</t>
+          <t>Đến đài phun nước ở Quảng trường Thành phố để tìm Echo mục tiêu</t>
         </is>
       </c>
     </row>
@@ -28998,7 +28998,7 @@
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t>Đến phía bắc Montelli Quarter để tìm Echo mục tiêu</t>
+          <t>Đến phía bắc Khu Montelli để tìm Echo mục tiêu</t>
         </is>
       </c>
     </row>
@@ -29128,7 +29128,7 @@
       </c>
       <c r="M439" t="inlineStr">
         <is>
-          <t>Đã nâng cấp tối đa Thể Lực Flight</t>
+          <t>Đã nâng cấp tối đa STA Bay</t>
         </is>
       </c>
     </row>
@@ -29262,7 +29262,7 @@
       <c r="M441" t="inlineStr">
         <is>
           <t>Ghi chú của Bác sĩ Đoàn Benir - R103
-Sau vài lần quan sát Roccia và nghiên cứu hành vi của cô, có vẻ như thuyền phó của chúng ta có cách giao tiếp với sinh vật kỳ lạ đó, &lt;te href=850122&gt;Pero&lt;/te&gt;. Nhờ Pero làm thông dịch, Roccia thậm chí còn có thể trò chuyện với những &lt;te href=850082&gt;Echoes&lt;/te&gt; khác. Điều thú vị là khả năng của cô dường như đang phát triển—ban đầu, cô cần nói chuyện trực tiếp với Echoes, nhưng giờ đây, có vẻ như cô có thể giao tiếp thông qua tần số.
+Sau vài lần quan sát Roccia và nghiên cứu hành vi của cô, có vẻ như thuyền phó của chúng ta có cách giao tiếp với sinh vật kỳ lạ đó, &lt;te href=850122&gt;Pero&lt;/te&gt;. Nhờ Pero làm thông dịch, Roccia thậm chí còn có thể trò chuyện với những &lt;te href=850082&gt;Echo&lt;/te&gt; khác. Điều thú vị là khả năng của cô dường như đang phát triển—ban đầu, cô cần nói chuyện trực tiếp với Echo, nhưng giờ đây, có vẻ như cô có thể giao tiếp thông qua tần số.
 Điều này chỉ bắt đầu sau khi cô gia nhập đoàn và gặp Pero, nên tôi đoán đó là một dạng cộng hưởng giữa họ, thứ mà cô học được trên đường đi. Chúng ta có thể gọi cô là Resonator phi bẩm sinh.
 P.S. Tất cả chỉ là phỏng đoán của tôi thôi. Với công cụ hiện có, tôi không thể xác định chính xác cô thuộc loại nào. Có khả năng nhỏ là Roccia không phải Resonator, mà chỉ tình cờ đồng điệu với một số tần số nhất định. Nhưng như vậy vẫn được coi là Resonator chứ? Tôi sẽ phải suy nghĩ thêm về điều này.</t>
         </is>
@@ -29329,7 +29329,7 @@
       </c>
       <c r="M442" t="inlineStr">
         <is>
-          <t>Mở Thiết bị đầu cuối Resonance ở Thành phố Ragunna để bắt đầu Nhiệm vụ Du hành</t>
+          <t>Mở Thiết bị đầu cuối Cộng Hưởng ở Thành phố Ragunna để bắt đầu Nhiệm vụ Du hành</t>
         </is>
       </c>
     </row>
@@ -29394,7 +29394,7 @@
       </c>
       <c r="M443" t="inlineStr">
         <is>
-          <t>Mở khóa Resonance Nexus trong Averardo Vault để bắt đầu Travel Quest</t>
+          <t>Mở khóa Mạng Lưới Cộng Hưởng trong Hầm Averardo để bắt đầu Nhiệm Vụ Du Hành</t>
         </is>
       </c>
     </row>
@@ -29459,7 +29459,7 @@
       </c>
       <c r="M444" t="inlineStr">
         <is>
-          <t>Mở Thiết bị đầu cuối Resonance ở Penitent's End để bắt đầu Nhiệm vụ Du hành</t>
+          <t>Mở Thiết bị đầu cuối Cộng Hưởng ở Penitent's End để bắt đầu Nhiệm vụ Du hành</t>
         </is>
       </c>
     </row>
@@ -29524,7 +29524,7 @@
       </c>
       <c r="M445" t="inlineStr">
         <is>
-          <t>Mở Thiết bị đầu cuối Resonance ở Hallowed Reach để bắt đầu Nhiệm vụ Du hành</t>
+          <t>Mở Thiết bị đầu cuối Cộng Hưởng ở Hallowed Reach để bắt đầu Nhiệm vụ Du hành</t>
         </is>
       </c>
     </row>
@@ -29589,7 +29589,7 @@
       </c>
       <c r="M446" t="inlineStr">
         <is>
-          <t>Mở Thiết bị đầu cuối Resonance ở Whisperwind Haven để bắt đầu Nhiệm vụ Du hành</t>
+          <t>Mở Thiết bị đầu cuối Cộng Hưởng ở Whisperwind Haven để bắt đầu Nhiệm vụ Du hành</t>
         </is>
       </c>
     </row>
@@ -29654,7 +29654,7 @@
       </c>
       <c r="M447" t="inlineStr">
         <is>
-          <t>Mở Thiết bị đầu cuối Resonance ở Nimbus Sanctum để bắt đầu Nhiệm vụ Du hành</t>
+          <t>Mở Thiết bị đầu cuối Cộng Hưởng ở Nimbus Sanctum để bắt đầu Nhiệm vụ Du hành</t>
         </is>
       </c>
     </row>
@@ -29719,7 +29719,7 @@
       </c>
       <c r="M448" t="inlineStr">
         <is>
-          <t>Mở Thiết bị đầu cuối Resonance ở Bán đảo Fagaceae để bắt đầu Nhiệm vụ Du hành</t>
+          <t>Mở Thiết bị đầu cuối Cộng Hưởng ở Bán đảo Fagaceae để bắt đầu Nhiệm vụ Du hành</t>
         </is>
       </c>
     </row>
@@ -29784,7 +29784,7 @@
       </c>
       <c r="M449" t="inlineStr">
         <is>
-          <t>Mở Thiết bị đầu cuối Resonance ở Thessaleo Fells để bắt đầu Nhiệm vụ Du hành</t>
+          <t>Mở Thiết bị đầu cuối Cộng Hưởng ở Thessaleo Fells để bắt đầu Nhiệm vụ Du hành</t>
         </is>
       </c>
     </row>
@@ -29982,10 +29982,10 @@
       </c>
       <c r="M452" t="inlineStr">
         <is>
-          <t>II. Overview Dự án Xây dựng
-Bối cảnh dự án: Sau trận phòng thủ Jinzhou, các công trình và cơ sở hạ tầng chịu thiệt hại nặng nề, hiện đã được sửa chữa sơ bộ. Dưới sự chỉ đạo của Quan Phủ và Ministry of Development, chúng tôi đã điều chỉnh Dự án Mở rộng Jinzhou Giai đoạn II, tích hợp những bài học từ trận chiến. Khu vực quy hoạch Giai đoạn II đã tăng gấp đôi so với Giai đoạn I, bao trùm phần lớn khu vực thành phố bị hư hại và các vùng chiến hào trong cuộc chiến. Theo kế hoạch điều chỉnh, mục tiêu đầu tiên là củng cố bố trí phòng thủ quanh khu vực ngoại thành bằng cách di dời các chiến hào về phía đông và nam, đồng thời dẫn nước biển vào để tạo thành vành đai phòng thủ bên ngoài. Thứ hai, chúng tôi đã lên kế hoạch xây dựng cấu trúc thẳng đứng mới cho nội thành Jinzhou, tạo địa hình chiến thuật thuận lợi và vùng đệm rút lui trong tình huống khẩn cấp, phù hợp với chiến lược "hàng phòng thủ sâu thứ hai" của Quan Phủ. Giai đoạn chuẩn bị dự án kéo dài 21 ngày. Sau khi được Phòng Kỹ thuật phê duyệt kế hoạch và sử dụng đất, chúng tôi đã sẵn sàng khởi công. Chúng tôi xin trình Quan Phủ phê duyệt lần cuối.
+          <t>II. Tổng quan Dự án Xây dựng
+Bối cảnh dự án: Sau trận phòng thủ Jinzhou, các công trình và cơ sở hạ tầng chịu thiệt hại nặng nề, hiện đã được sửa chữa sơ bộ. Dưới sự chỉ đạo của Quan Phủ và Bộ Phát Triển, chúng tôi đã điều chỉnh Dự án Mở rộng Jinzhou Giai đoạn II, tích hợp những bài học từ trận chiến. Khu vực quy hoạch Giai đoạn II đã tăng gấp đôi so với Giai đoạn I, bao trùm phần lớn khu vực thành phố bị hư hại và các vùng chiến hào trong cuộc chiến. Theo kế hoạch điều chỉnh, mục tiêu đầu tiên là củng cố bố trí phòng thủ quanh khu vực ngoại thành bằng cách di dời các chiến hào về phía đông và nam, đồng thời dẫn nước biển vào để tạo thành vành đai phòng thủ bên ngoài. Thứ hai, chúng tôi đã lên kế hoạch xây dựng cấu trúc thẳng đứng mới cho nội thành Jinzhou, tạo địa hình chiến thuật thuận lợi và vùng đệm rút lui trong tình huống khẩn cấp, phù hợp với chiến lược "hàng phòng thủ sâu thứ hai" của Quan Phủ. Giai đoạn chuẩn bị dự án kéo dài 21 ngày. Sau khi được Phòng Kỹ thuật phê duyệt kế hoạch và sử dụng đất, chúng tôi đã sẵn sàng khởi công. Chúng tôi xin trình Quan Phủ phê duyệt lần cuối.
 Kính trình,
-Đội Phát triển Đất đai, Ban Cơ sở Hạ tầng, Ministry of Development</t>
+Đội Phát triển Đất đai, Ban Cơ sở Hạ tầng, Bộ Phát Triển</t>
         </is>
       </c>
     </row>
@@ -30059,15 +30059,15 @@
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t>&lt;i&gt;Report số: 94001&lt;/i&gt;
+          <t>&lt;i&gt;Báo cáo số: 94001&lt;/i&gt;
 Sau những chuẩn bị kỹ lưỡng, cuối cùng chúng tôi cũng vượt qua Desorock Highland và đặt chân đến Thung lũng Norfall trong vòng hai tuần.
 Tuy nhiên, do sự hiện diện của Rào chắn Groundwave, ngay cả với trang bị bảo hộ chuyên dụng, chúng tôi cũng không thể triển khai toàn bộ lực lượng vào thung lũng cùng lúc. Vì vậy, đội Tuần thám được phái đi trước để trinh sát và chuẩn bị cho thời khắc mà Đại tướng cùng Sentinel đã tiên đoán.
-Trong Trận chiến Dưới Trăng Lưỡi Liềm, vầng trăng định mệnh treo cao trên bầu trời... Trận chiến ấy giờ đã thuộc về quá khứ, thế nhưng khi trở lại thung lũng này, tiếng kêu thảm thiết vẫn còn vương vấn trong không khí. Không ai biết đó là mô phỏng của TD hay "bóng ma" của những chiến binh đã ngã xuống... Vô số binh lính đã chết trong đau đớn và tuyệt vọng không thể tưởng tượng nổi trong cuộc chiến đó, nơi đồng minh và kẻ thù không thể phân biệt. Ta khó lòng nhớ lại những khoảnh khắc ấy... Dưới sự thúc ép của Đại tướng Jiyan, Huaxu Academy đã phát triển thuốc giải Retroact Rain, nghĩa là chúng ta không hoàn toàn bất lực. Nhưng khi Retroact Rain bị lực lượng Threnodian tăng cường, chỉ những người sở hữu năng lực Resonance mới chịu đựng được áp lực khủng khiếp lên tâm trí. Những người lính bình thường không thể gánh nổi sức nặng nghiền nát ấy...
+Trong Trận chiến Dưới Trăng Lưỡi Liềm, vầng trăng định mệnh treo cao trên bầu trời... Trận chiến ấy giờ đã thuộc về quá khứ, thế nhưng khi trở lại thung lũng này, tiếng kêu thảm thiết vẫn còn vương vấn trong không khí. Không ai biết đó là mô phỏng của TD hay "bóng ma" của những chiến binh đã ngã xuống... Vô số binh lính đã chết trong đau đớn và tuyệt vọng không thể tưởng tượng nổi trong cuộc chiến đó, nơi đồng minh và kẻ thù không thể phân biệt. Ta khó lòng nhớ lại những khoảnh khắc ấy... Dưới sự thúc ép của Đại tướng Jiyan, Học viện Huaxu đã phát triển thuốc giải Retroact Rain, nghĩa là chúng ta không hoàn toàn bất lực. Nhưng khi Retroact Rain bị lực lượng Threnodian tăng cường, chỉ những người sở hữu năng lực Cộng Hưởng mới chịu đựng được áp lực khủng khiếp lên tâm trí. Những người lính bình thường không thể gánh nổi sức nặng nghiền nát ấy...
 Do tình báo hạn chế và những quyết định liều lĩnh, chúng ta đã phải trả giá đắt trong Trận chiến Dưới Trăng Lưỡi Liềm. Đại tướng Jiyan dẫn chúng ta vượt qua một khe hẹp ra khỏi Vùng đất hoang Norfall, lập nên Căn cứ Tiền tiêu ngay bên ngoài Thung lũng Norfall, nơi chúng ta đã trụ vững kể từ đó. Chúng ta không thể để thảm kịch ấy lặp lại.
 Đại tướng Jiyan đã thu hút sự chú ý của hầu hết TD bên ngoài Thung lũng Norfall, giúp chúng ta có thời gian quý báu để trinh sát. Rào chắn Groundwave làm gián đoạn mọi tín hiệu liên lạc, vì vậy nếu ai đó bị tách khỏi đội hình chính, hệ thống định vị sẽ không thể theo dõi họ nữa. Lạc bước ở đây đồng nghĩa với án tử. Từ giờ trở đi, chúng ta phải tự lực cánh sinh. Mỗi bước đi đều phải cực kỳ thận trọng.
 ...
-Sau hành trình dài đầy gian khổ, phải che giấu dấu vết, Dodge TD và chịu đựng áp lực của Rào chắn Groundwave, cả đội đã kiệt sức. Nhưng cuối cùng, chúng ta cũng đã đến được vách đá.
-Theo những gì quan sát được trên đường, giao thông trong Thung lũng Norfall bị hạn chế nghiêm trọng—quá hẹp để triển khai các cỗ máy quân sự lớn, đặc biệt là với nguy cơ đá rơi liên tục. Nếu xung đột nổ ra ở đây, việc người bình thường điều khiển các cỗ máy Tacetite nặng nề gần như bất khả thi. Đây hẳn là lý do Đại tướng Jiyan thay đổi chiến thuật, chỉ cho phép những Resonators sở hữu Năng lượng Resonance gia nhập Căn cứ Tiền tiêu.
+Sau hành trình dài đầy gian khổ, phải che giấu dấu vết, né tránh TD và chịu đựng áp lực của Rào chắn Groundwave, cả đội đã kiệt sức. Nhưng cuối cùng, chúng ta cũng đã đến được vách đá.
+Theo những gì quan sát được trên đường, giao thông trong Thung lũng Norfall bị hạn chế nghiêm trọng—quá hẹp để triển khai các cỗ máy quân sự lớn, đặc biệt là với nguy cơ đá rơi liên tục. Nếu xung đột nổ ra ở đây, việc người bình thường điều khiển các cỗ máy Tacetite nặng nề gần như bất khả thi. Đây hẳn là lý do Đại tướng Jiyan thay đổi chiến thuật, chỉ cho phép những Resonator sở hữu Năng lượng Cộng Hưởng gia nhập Căn cứ Tiền tiêu.
 Nhìn về phía sâu thẳm của Vùng đất hoang Norfall, ta thấy Những Tàn tích vẫn lơ lửng ở đằng xa. Chúng tôi thiết lập thiết bị trinh sát tầm xa, phát hiện một đàn TD đang di chuyển bất an giữa những tiếng thét ma quái vang vọng khắp nơi. Âm thanh ấy gợi nhớ đến con quái vật trong Trận chiến Dưới Trăng Lưỡi Liềm.</t>
         </is>
       </c>
@@ -30140,12 +30140,12 @@
       <c r="M454" t="inlineStr">
         <is>
           <t>Chúng tôi đã thu thập thông tin về Ovathrax. Trong Trận Chiến Dưới Lưỡi Liềm, con quái vật đó đã cướp đi vô số sinh mạng, và kinh hoàng hơn... chúng tôi thấy nó bắt chước lại kiếm pháp và chiến thuật của chúng ta. Khả năng này giống với khả năng đã ghi nhận của Ovathrax là "hấp thụ tần số chiến đấu để tăng cường sức mạnh". Nhưng liệu đó có thật sự là Ovathrax? Theo hồ sơ chúng tôi tổng hợp, tần số và tư thế của sinh vật đó lại gần với Crownless hơn. Rất có thể, đó chỉ là một đội tiên phong do Ovathrax phái đi.
-Sau khi rút lui về ngoại ô Norfall Valley, nó ngừng tấn công, cho thấy mục đích thực sự của nó là tích lũy sức mạnh—nuôi dưỡng sự tiến hóa của Ovathrax và câu giờ cho sự xuất hiện cuối cùng của nó. Trận Chiến Dưới Lưỡi Liềm có lẽ đã trở thành bữa tiệc của nó.
+Sau khi rút lui về ngoại ô Thung Lũng Norfall, nó ngừng tấn công, cho thấy mục đích thực sự của nó là tích lũy sức mạnh—nuôi dưỡng sự tiến hóa của Ovathrax và câu giờ cho sự xuất hiện cuối cùng của nó. Trận Chiến Dưới Lưỡi Liềm có lẽ đã trở thành bữa tiệc của nó.
 ...
-Sau khi trinh sát Khu Suspended Ruins, đội đã quan sát thấy một ánh sáng tím nhạt nhấp nháy theo một kiểu riêng biệt. Có ai khác từng để ý đến hiện tượng này chưa? Liệu Rào Chắn Sóng Mặt Đất có che giấu sự hiện diện của nó không? Đó có phải là tín hiệu cầu cứu không? Liệu vẫn còn người sống sót ở Norfall Barrens? Thế nhưng, tần số nhấp nháy ấy khiến tôi cảm thấy bất an...
-Sau khi thảo luận, đội quyết định tiến về phía trước và xuống Vách Đá Norfall để tiếp cận Khu Suspended Ruins. Nhưng khi xuống đến nơi, cảm giác bất an ấy lại quay về. Chúng tôi nhận ra ánh sáng tím dường như đang theo dõi chúng tôi. Tần số nhấp nháy khiến tôi khó chịu, như thể có thứ gì đó đang chớp mắt, như thể nó đang theo dõi chúng tôi...
+Sau khi trinh sát Khu Tàn Tích Lơ Lửng, đội đã quan sát thấy một ánh sáng tím nhạt nhấp nháy theo một kiểu riêng biệt. Có ai khác từng để ý đến hiện tượng này chưa? Liệu Rào Chắn Sóng Mặt Đất có che giấu sự hiện diện của nó không? Đó có phải là tín hiệu cầu cứu không? Liệu vẫn còn người sống sót ở Bãi Hoang Norfall? Thế nhưng, tần số nhấp nháy ấy khiến tôi cảm thấy bất an...
+Sau khi thảo luận, đội quyết định tiến về phía trước và xuống Vách Đá Norfall để tiếp cận Khu Tàn Tích Lơ Lửng. Nhưng khi xuống đến nơi, cảm giác bất an ấy lại quay về. Chúng tôi nhận ra ánh sáng tím dường như đang theo dõi chúng tôi. Tần số nhấp nháy khiến tôi khó chịu, như thể có thứ gì đó đang chớp mắt, như thể nó đang theo dõi chúng tôi...
 Hồ sơ lưu trữ tại Tòa Thị Chính:
-Outriders đã hoàn thành phần lớn công tác trinh sát Norfall Valley. Tuy nhiên, khi xuống vách đá, họ gặp phải sự can nhiễu từ một tần số lạ. Sự nhiễu loạn này dẫn đến một cuộc phục kích bởi một lượng lớn TD. Theo báo cáo của Tướng Jiyan, ông đã cảm nhận tình hình qua gió và ra lệnh phối hợp cho lực lượng phía sau. Sau đó, ông phá vỡ Rào Chắn Sóng Mặt Đất và giải cứu đội thành công. May mắn thay, không có thương vong nào trong đội, dù một số thiết bị đã bị thất lạc. Tuy nhiên, việc phá vỡ Rào Chắn Sóng Mặt Đất đã gây tổn thương nhiều cơ quan nội tạng cho Tướng Jiyan. Trong Cooldown phục, ông vẫn ở lại Căn Cứ Tiền Tuyến.</t>
+Đội Tuần Duyên đã hoàn thành phần lớn công tác trinh sát Thung Lũng Norfall. Tuy nhiên, khi xuống vách đá, họ gặp phải sự can nhiễu từ một tần số lạ. Sự nhiễu loạn này dẫn đến một cuộc phục kích bởi một lượng lớn TD. Theo báo cáo của Tướng Jiyan, ông đã cảm nhận tình hình qua gió và ra lệnh phối hợp cho lực lượng phía sau. Sau đó, ông phá vỡ Rào Chắn Sóng Mặt Đất và giải cứu đội thành công. May mắn thay, không có thương vong nào trong đội, dù một số thiết bị đã bị thất lạc. Tuy nhiên, việc phá vỡ Rào Chắn Sóng Mặt Đất đã gây tổn thương nhiều cơ quan nội tạng cho Tướng Jiyan. Trong thời gian hồi phục, ông vẫn ở lại Căn Cứ Tiền Tuyến.</t>
         </is>
       </c>
     </row>
@@ -30217,9 +30217,9 @@
       </c>
       <c r="M455" t="inlineStr">
         <is>
-          <t>&lt;i&gt;Report về Lampylumen&lt;/i&gt;
+          <t>&lt;i&gt;Báo cáo về Lampylumen&lt;/i&gt;
 Mỏ Hổ Hàm chủ yếu sản xuất Lampylumen cùng các loại quặng khác, cũng như một lượng nhỏ quặng Tacetite.
-Sau nhiều năm nghiên cứu chung giữa Huaxu Academy và Bộ Phát triển, một kết luận thống nhất đã được đưa ra về sự hình thành của Hổ Hàm.
+Sau nhiều năm nghiên cứu chung giữa Học viện Huaxu và Bộ Phát triển, một kết luận thống nhất đã được đưa ra về sự hình thành của Hổ Hàm.
 Họ phát hiện rằng sự dịch chuyển kiến tạo do Hiện tượng Waveworn gây ra đã làm thay đổi cấu trúc địa tầng ở Jinzhou, đẩy các mỏ quặng hình thành từ hàng chục triệu năm trước lên vỏ trái đất và đưa Lampylumen vào tầm hiểu biết của con người.
 Khảo sát ban đầu về các mạch Lampylumen đã đưa ra những kết luận sau:
 Hình dạng: Lampylumen thường có cấu trúc lập phương, thường thấy dưới dạng khối đơn hoặc xếp chồng, hình chữ nhật giúp dễ dàng khai thác. Nó nóng chảy ở nhiệt độ cao, dễ dàng tạo hình.
@@ -30295,7 +30295,7 @@
           <t>["Thác Nước Hùng Vĩ Của Tự Nhiên" Suối Tuyết]
 Núi Firmament là nơi có nhiều suối nước nóng tự nhiên, và Suối Tuyết thơ mộng chính là nguồn cung cấp nước nóng cho Hongzhen. Những cành cây của một cây hoa nở rộ ôm lấy dòng thác đổ từ vách đá, nuôi dưỡng toàn bộ hệ thống suối nước nóng của Hongzhen.
 Cây này được những cư dân đầu tiên của Hongzhen trồng khi thị trấn mới thành lập. Qua thời gian, nó đã vươn lên từ một khe nứt trên đá và giờ đây sừng sững hiên ngang. Những dòng thác không ngừng đập vào vách núi đã dần mài mòn những tảng đá cứng thành những bề mặt tròn nhẵn.
-Sau này, người dân Hongzhen hiện đại đã cải tạo cảnh quan để tái hiện lại truyền thuyết về Suối Tuyết trên núi Firmament. Vài thế kỷ trước, một nhân vật bí ẩn đi qua vùng này khi một trận bão tuyết lớn phong tỏa các con đèo. Thấy củi lửa của dân làng sắp cạn kiệt, người lữ khách đã dùng sức mạnh Resonance để khắc một lối đi xuyên núi và chuyển dòng suối từ trên cao xuống làng. Trong khoảnh khắc, sương mù và băng tan chảy theo dòng nước chảy về phía tây, tạo nên cảnh tượng kỳ vĩ như tiên nữ lướt trên mặt nước.</t>
+Sau này, người dân Hongzhen hiện đại đã cải tạo cảnh quan để tái hiện lại truyền thuyết về Suối Tuyết trên núi Firmament. Vài thế kỷ trước, một nhân vật bí ẩn đi qua vùng này khi một trận bão tuyết lớn phong tỏa các con đèo. Thấy củi lửa của dân làng sắp cạn kiệt, người lữ khách đã dùng sức mạnh Cộng Hưởng để khắc một lối đi xuyên núi và chuyển dòng suối từ trên cao xuống làng. Trong khoảnh khắc, sương mù và băng tan chảy theo dòng nước chảy về phía tây, tạo nên cảnh tượng kỳ vĩ như tiên nữ lướt trên mặt nước.</t>
         </is>
       </c>
     </row>
@@ -30365,7 +30365,7 @@
       </c>
       <c r="M457" t="inlineStr">
         <is>
-          <t>5. Những "Sứ Giả Thần Linh" xuất hiện trong phim tài liệu thực chất do các Echoes từ Thiết bị đầu cuối Dự phòng thủ vai, vì Hội Huấn từ chối cho phép các Sứ Giả Thần Linh thật tham gia bất kỳ hoạt động quay phim giải trí nào.
+          <t>5. Những "Sứ Giả Thần Linh" xuất hiện trong phim tài liệu thực chất do các Echo từ Thiết bị đầu cuối Dự phòng thủ vai, vì Hội Huấn từ chối cho phép các Sứ Giả Thần Linh thật tham gia bất kỳ hoạt động quay phim giải trí nào.
 6. Những cảnh chiến đấu giữa Napoli đệ Nhị và Thánh Nữ phần lớn do các nhà tài trợ đảm nhận, đa số là nhân viên hợp đồng của Lollo Logistics. Người dân địa phương ở Rinascita chỉ đóng một phần nhỏ trong dàn diễn viên, nhưng họ đã dành cả ngày để dạy các nhân viên giao hàng cách xông pha vào kẻ thù như những hiệp sĩ thực thụ.
 7. Trong cảnh ẩu đả ở quán bar, đạo diễn đã trực tiếp chỉ đạo vũ đạo chiến đấu sau khi uống quá nhiều rượu đặc sản từ Bán đảo Fagaceae.
 8. Cảnh con tàu Pilgrim's Sail đầu tiên khởi hành được quay chỉ trong một lần duy nhất vì đoàn làm phim chỉ thuê được tàu trong nửa ngày.
@@ -30436,8 +30436,8 @@
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t>Resonance Beacon ghi lại dữ liệu từ khu vực xung quanh và truyền về Resonance Nexus để phân tích.
-Bạn có thể dịch chuyển tức thời đến bất kỳ Resonance Beacon nào đã kích hoạt, nơi Resonators bị thương hoặc bất tỉnh sẽ được hồi phục.</t>
+          <t>Điểm Cộng Hưởng ghi lại dữ liệu từ khu vực xung quanh và truyền về Mạng Lưới Cộng Hưởng để phân tích.
+Bạn có thể dịch chuyển tức thời đến bất kỳ Điểm Cộng Hưởng nào đã kích hoạt, nơi Resonator bị thương hoặc bất tỉnh sẽ được hồi phục.</t>
         </is>
       </c>
     </row>
@@ -30567,7 +30567,7 @@
       </c>
       <c r="M460" t="inlineStr">
         <is>
-          <t>Biến thành Hoartoise trong 4 giây, mỗi giây gây 937.50% Glacio DMG và hất tung kẻ địch xung quanh. Hồi chiêu: 15 giây.</t>
+          <t>Biến hình thành Hoartoise trong 4 giây, mỗi giây gây 937.50% Sát Thương Glacio và hất tung kẻ địch xung quanh. Thời gian hồi: 15 giây.</t>
         </is>
       </c>
     </row>
@@ -30697,7 +30697,7 @@
       </c>
       <c r="M462" t="inlineStr">
         <is>
-          <t>Khi Resonators trang bị Hoartoise sử dụng Outro Skill, Cooldown chiêu của Kỹ Năng Echo sẽ được đặt lại.</t>
+          <t>Khi Resonator trang bị Hoartoise sử dụng Kỹ Năng Outro, Thời gian hồi chiêu của Kỹ Năng Echo sẽ được đặt lại.</t>
         </is>
       </c>
     </row>
@@ -30762,7 +30762,7 @@
       </c>
       <c r="M463" t="inlineStr">
         <is>
-          <t>Summon Glacio Prism trong 6 giây để tấn công kẻ địch. Mỗi đòn gây 436,67% Glacio DMG, tăng thêm 66,67% nếu mục tiêu bị Đóng Băng. Hồi chiêu: 15 giây.</t>
+          <t>Triệu hồi Lăng Kính Glacio trong 6 giây để tấn công kẻ địch. Mỗi đòn gây 436,67% Sát Thương Glacio, tăng thêm 66,67% nếu mục tiêu bị Đóng Băng. Thời gian hồi: 15 giây.</t>
         </is>
       </c>
     </row>
@@ -30957,7 +30957,7 @@
       </c>
       <c r="M466" t="inlineStr">
         <is>
-          <t>Biến thành Autopuppet Scout để đóng băng kẻ địch xung quanh trong 3 giây, gây 1146.67% Glacio DMG. Cooldown chiêu: 15 giây.</t>
+          <t>Biến hình thành Autopuppet Scout để đóng băng kẻ địch xung quanh trong 3 giây, gây 1146.67% Sát Thương Glacio. Thời gian hồi chiêu: 15 giây.</t>
         </is>
       </c>
     </row>
@@ -31022,7 +31022,7 @@
       </c>
       <c r="M467" t="inlineStr">
         <is>
-          <t>Kẻ địch bị đóng băng sẽ gây ít hơn 50.00% sát thương trong 6 giây sau khi trạng thái Đông Cứng kết thúc.</t>
+          <t>Kẻ địch bị đóng băng sẽ gây ít hơn 50.00% DMG trong 6 giây sau khi trạng thái Đông Cứng kết thúc.</t>
         </is>
       </c>
     </row>
@@ -31087,7 +31087,7 @@
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>Increase thời gian trạng thái Bị Đông cứng thêm 3 giây.</t>
+          <t>Tăng thời gian trạng thái Bị Đông cứng thêm 3 giây.</t>
         </is>
       </c>
     </row>
@@ -31152,7 +31152,7 @@
       </c>
       <c r="M469" t="inlineStr">
         <is>
-          <t>Summon Gulpuff tạo ra trường hồi phục. Tất cả đồng đội trong phạm vi này phục hồi 25,00% HP. Hồi chiêu: 20 giây.</t>
+          <t>Triệu hồi Gulpuff tạo ra trường hồi phục. Tất cả đồng đội trong phạm vi này phục hồi 25,00% HP. Thời gian hồi: 20 giây.</t>
         </is>
       </c>
     </row>
@@ -31217,7 +31217,7 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>Biến thành Rocksteady Guardian để thu hút sự chú ý của kẻ địch xung quanh. Ban cho các thành viên trong đội gần đó một lớp Khiên dựa trên 20.00% HP Tối Đa của người sử dụng trong 10 giây. Hồi chiêu: 20 giây.</t>
+          <t>Biến hình thành Rocksteady Guardian để thu hút sự chú ý của kẻ địch xung quanh. Ban cho các thành viên trong đội gần đó một lớp Khiên dựa trên 20.00% HP Tối Đa của người sử dụng trong 10 giây. Thời gian hồi: 20 giây.</t>
         </is>
       </c>
     </row>
@@ -31347,7 +31347,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>Sức mạnh khiên dựa trên 60.00% HP tối đa của Resonator.</t>
+          <t>Sức mạnh khiên dựa trên 60.00% HP tối đa của Cộng Hưởng Giả.</t>
         </is>
       </c>
     </row>
@@ -31412,7 +31412,7 @@
       </c>
       <c r="M473" t="inlineStr">
         <is>
-          <t>Summon Whiff Whaff hút kẻ địch xung quanh vào trung tâm trong 5 giây, gây 131.67% Aero DMG 12 lần. Hồi chiêu: 20 giây.</t>
+          <t>Triệu hồi Whiff Whaff hút kẻ địch xung quanh vào trung tâm trong 5 giây, gây 131.67% Sát Thương Aero 12 lần. Thời gian hồi: 20 giây.</t>
         </is>
       </c>
     </row>
@@ -31477,7 +31477,7 @@
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>Kẻ địch bị kéo vào sẽ chịu thêm 30.00% sát thương.</t>
+          <t>Kẻ địch bị kéo vào sẽ chịu thêm 30.00% DMG.</t>
         </is>
       </c>
     </row>
@@ -31542,7 +31542,7 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>Biến thành Dreamless để gây 1397.00% Havoc DMG. Increase Tấn Công cho tất cả thành viên trong đội gần đó thêm 30.00%. Hồi chiêu: 20 giây.</t>
+          <t>Biến hình thành Dreamless để gây 1397.00% Sát Thương Havoc. Tăng ATK cho tất cả thành viên trong đội gần đó thêm 30.00%. Thời gian hồi: 20 giây.</t>
         </is>
       </c>
     </row>
@@ -31672,7 +31672,7 @@
       </c>
       <c r="M477" t="inlineStr">
         <is>
-          <t>Tạo ra 4 Concerto Energy mỗi giây.</t>
+          <t>Tạo ra 4 Năng Lượng Giao Hưởng mỗi giây.</t>
         </is>
       </c>
     </row>
@@ -31737,7 +31737,7 @@
       </c>
       <c r="M478" t="inlineStr">
         <is>
-          <t>Biến thành Feilian Beringal và đập mạnh xuống đất, gây 800.00% Aero DMG và để lại một cột trụ trong 9 giây. Cột trụ giải phóng sóng xung kích mỗi 3 giây, gây 816.00% Aero DMG. Hồi chiêu: 20 giây.</t>
+          <t>Biến hình thành Feilian Beringal và đập mạnh xuống đất, gây 800.00% Sát Thương Aero và để lại một cột trụ trong 9 giây. Cột trụ giải phóng sóng xung kích mỗi 3 giây, gây 816.00% Sát Thương Aero. Thời gian hồi: 20 giây.</t>
         </is>
       </c>
     </row>
@@ -31867,7 +31867,7 @@
       </c>
       <c r="M480" t="inlineStr">
         <is>
-          <t>Biến thành Impermanence Heron, phun lửa xuống dưới gây 1032.00% Sát Thương Hệ Havoc và tạo ra một vùng lửa cháy trong 5 giây. Kẻ địch trong vùng chịu 623.70% Sát Thương Hệ Havoc mỗi giây và bị giảm 40% Movement Speed. Hồi chiêu: 15 giây.</t>
+          <t>Biến hình thành Impermanence Heron, phun lửa xuống dưới gây 1032.00% Sát Thương Hệ Havoc và tạo ra một vùng lửa cháy trong 5 giây. Kẻ địch trong vùng chịu 623.70% Sát Thương Hệ Havoc mỗi giây và bị giảm 40% Tốc Độ Di Chuyển. Thời gian hồi: 15 giây.</t>
         </is>
       </c>
     </row>
@@ -31932,7 +31932,7 @@
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>Khi rời khỏi vùng thiêu đốt, kẻ địch tiếp tục chịu sát thương và tốc độ di chuyển bị giảm trong 3 giây.</t>
+          <t>Khi rời khỏi vùng thiêu đốt, kẻ địch tiếp tục chịu DMG và tốc độ di chuyển bị giảm trong 3 giây.</t>
         </is>
       </c>
     </row>
@@ -32257,7 +32257,7 @@
       </c>
       <c r="M486" t="inlineStr">
         <is>
-          <t>Cấp Kỹ năng 5</t>
+          <t>Cấp Kỹ Năng 5</t>
         </is>
       </c>
     </row>
@@ -32322,7 +32322,7 @@
       </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t>Cấp Kỹ năng 6</t>
+          <t>Cấp Kỹ Năng 6</t>
         </is>
       </c>
     </row>
@@ -32387,7 +32387,7 @@
       </c>
       <c r="M488" t="inlineStr">
         <is>
-          <t>Cấp Kỹ năng 7</t>
+          <t>Cấp Kỹ Năng 7</t>
         </is>
       </c>
     </row>
@@ -32452,7 +32452,7 @@
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t>Cấp Kỹ năng 8</t>
+          <t>Cấp Kỹ Năng 8</t>
         </is>
       </c>
     </row>
@@ -32517,7 +32517,7 @@
       </c>
       <c r="M490" t="inlineStr">
         <is>
-          <t>Tấn Công của Resonator này +10%</t>
+          <t>ATK của Resonator này +10%</t>
         </is>
       </c>
     </row>
@@ -32582,7 +32582,7 @@
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t>Skill Echo này giảm 10% Cooldown chiêu.</t>
+          <t>Kỹ năng Echo này giảm 10% Thời gian hồi chiêu.</t>
         </is>
       </c>
     </row>
@@ -32647,7 +32647,7 @@
       </c>
       <c r="M492" t="inlineStr">
         <is>
-          <t>Tấn Công của Resonator này +10%</t>
+          <t>ATK của Resonator này +10%</t>
         </is>
       </c>
     </row>
@@ -32712,7 +32712,7 @@
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>Skill Echo này giảm 10% Cooldown chiêu.</t>
+          <t>Kỹ năng Echo này giảm 10% Thời gian hồi chiêu.</t>
         </is>
       </c>
     </row>
